--- a/Simulador_Riesgos_Costco_BlackSwan.xlsx
+++ b/Simulador_Riesgos_Costco_BlackSwan.xlsx
@@ -5,15 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tiendasmd-my.sharepoint.com/personal/luismayala_md_com_sv/Documents/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luism\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="8_{3EF926AF-F58E-4E90-909C-8EBFFC9DD33D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65D69FDC-7A6A-478B-B292-8B6118EDB9D6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32F193BB-87A0-4F7B-B9D0-FBA383A0CE77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Matriz de Sensibilidad" sheetId="1" r:id="rId1"/>
+    <sheet name="Monte Carlo" sheetId="2" r:id="rId2"/>
+    <sheet name="Tornado — Cisnes Negros" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -73,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="143">
   <si>
     <t>🦢  SIMULADOR DE RIESGOS COSTCO — Black Swan Edition</t>
   </si>
@@ -240,29 +242,284 @@
     <t>⚠  Solo con fines educativos / análisis de inversión personal. No constituye asesoramiento financiero. | Fuentes: Precio y P/E: Bloomberg/FactSet May 2026 | Modelo: Tiendas MD Investment Research</t>
   </si>
   <si>
+    <t>🎲  SIMULACIÓN MONTE CARLO — Distribución del Fair Value (COST)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ⚙  PARÁMETROS DE SIMULACIÓN  (N = 2,000 iteraciones)</t>
+  </si>
+  <si>
+    <t>Precio Actual (COST)</t>
+  </si>
+  <si>
+    <t>← modifica</t>
+  </si>
+  <si>
+    <t>Precio spot May 2026. Source: Bloomberg, May 2026</t>
+  </si>
+  <si>
+    <t>P/E Actual</t>
+  </si>
+  <si>
+    <t>Consenso de mercado. Source: FactSet, May 2026</t>
+  </si>
+  <si>
+    <t>P/E Medio (μ)</t>
+  </si>
+  <si>
+    <t>Media histórica 5Y ajustada</t>
+  </si>
+  <si>
+    <t>P/E Desv. Estándar (σ)</t>
+  </si>
+  <si>
+    <t>Volatilidad implícita del múltiplo</t>
+  </si>
+  <si>
+    <t>Shock Tasa Medio (μ)</t>
+  </si>
+  <si>
+    <t>Escenario base Fed +100bps</t>
+  </si>
+  <si>
+    <t>Shock Tasa Desv. (σ)</t>
+  </si>
+  <si>
+    <t>Dispersión de escenarios macro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  📊  RESULTADOS ESTADÍSTICOS  (Fair Value Simulado)</t>
+  </si>
+  <si>
+    <t>Métrica</t>
+  </si>
+  <si>
+    <t>Valor</t>
+  </si>
+  <si>
+    <t>Interpretación</t>
+  </si>
+  <si>
+    <t>Fair Value Esperado (μ)</t>
+  </si>
+  <si>
+    <t>Promedio de 2,000 simulaciones. Referencia central del modelo.</t>
+  </si>
+  <si>
+    <t>Mediana Fair Value</t>
+  </si>
+  <si>
+    <t>50% de simulaciones caen por debajo de este valor.</t>
+  </si>
+  <si>
+    <t>Desviación Estándar (σ)</t>
+  </si>
+  <si>
+    <t>Dispersión de posibles Fair Values. Mayor σ = mayor incertidumbre.</t>
+  </si>
+  <si>
+    <t>Percentil 5% (Worst Case)</t>
+  </si>
+  <si>
+    <t>Solo el 5% de escenarios dan un precio menor. Proxy de 'tail risk'.</t>
+  </si>
+  <si>
+    <t>Percentil 25%</t>
+  </si>
+  <si>
+    <t>Cuartil inferior — escenario pesimista moderado.</t>
+  </si>
+  <si>
+    <t>Percentil 75%</t>
+  </si>
+  <si>
+    <t>Cuartil superior — escenario optimista moderado.</t>
+  </si>
+  <si>
+    <t>Percentil 95% (Best Case)</t>
+  </si>
+  <si>
+    <t>Solo el 5% de escenarios superan este precio.</t>
+  </si>
+  <si>
+    <t>Probabilidad de Pérdida vs $780</t>
+  </si>
+  <si>
+    <t>% de escenarios donde Fair Value &lt; Precio Actual.</t>
+  </si>
+  <si>
+    <t>Probabilidad Upside &gt;10%</t>
+  </si>
+  <si>
+    <t>% de escenarios donde Fair Value &gt; $858 (+10%).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  📈  HISTOGRAMA DE DISTRIBUCIÓN  (Fair Value Simulado — 2,000 iteraciones)</t>
+  </si>
+  <si>
+    <t>Rango Fair Value</t>
+  </si>
+  <si>
+    <t>Frecuencia (#sims)</t>
+  </si>
+  <si>
+    <t>Frecuencia (%)</t>
+  </si>
+  <si>
+    <t>$169</t>
+  </si>
+  <si>
+    <t>$217</t>
+  </si>
+  <si>
+    <t>$264</t>
+  </si>
+  <si>
+    <t>$312</t>
+  </si>
+  <si>
+    <t>$359</t>
+  </si>
+  <si>
+    <t>$407</t>
+  </si>
+  <si>
+    <t>$454</t>
+  </si>
+  <si>
+    <t>$502</t>
+  </si>
+  <si>
+    <t>$549</t>
+  </si>
+  <si>
+    <t>$597</t>
+  </si>
+  <si>
+    <t>$644</t>
+  </si>
+  <si>
+    <t>$692</t>
+  </si>
+  <si>
+    <t>$739</t>
+  </si>
+  <si>
+    <t>$787</t>
+  </si>
+  <si>
+    <t>$834</t>
+  </si>
+  <si>
+    <t>$882</t>
+  </si>
+  <si>
+    <t>$929</t>
+  </si>
+  <si>
+    <t>$977</t>
+  </si>
+  <si>
+    <t>$1024</t>
+  </si>
+  <si>
+    <t>$1072</t>
+  </si>
+  <si>
+    <t>$1119</t>
+  </si>
+  <si>
+    <t>🌪  TORNADO — Impacto de Cisnes Negros en Fair Value (COST)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Sensibilidad del Fair Value ante cada factor de riesgo — Base: $780 (P/E 50x, tasa base)</t>
+  </si>
+  <si>
+    <t>Factor de Riesgo</t>
+  </si>
+  <si>
+    <t>FV Pesimista</t>
+  </si>
+  <si>
+    <t>FV Base</t>
+  </si>
+  <si>
+    <t>FV Optimista</t>
+  </si>
+  <si>
+    <t>Δ Bajo</t>
+  </si>
+  <si>
+    <t>Δ Alto</t>
+  </si>
+  <si>
+    <t>Rango Total</t>
+  </si>
+  <si>
+    <t>Disrupción Membresías (−80% Op.Income)</t>
+  </si>
+  <si>
+    <t>P/E Compresión a 15x (Retail)</t>
+  </si>
+  <si>
+    <t>Crisis Kirkland (−40% EPS)</t>
+  </si>
+  <si>
+    <t>Bloqueo Pacífico (−25% Revenue)</t>
+  </si>
+  <si>
+    <t>Entrada Amazon (−15% Market Share)</t>
+  </si>
+  <si>
+    <t>Compresión P/E moderada (35x)</t>
+  </si>
+  <si>
+    <t>Shock de Tasa +5% (Pánico Fed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  🔍  LECTURA DEL GRÁFICO TORNADO</t>
+  </si>
+  <si>
+    <t>1. Las barras ROJAS muestran el impacto negativo máximo de cada cisne negro en el Fair Value vs. el precio base de $780.</t>
+  </si>
+  <si>
+    <t>2. Las barras VERDES muestran el upside máximo si el factor se resuelve favorablemente.</t>
+  </si>
+  <si>
+    <t>3. El factor con la barra MÁS LARGA es el mayor driver de riesgo — donde el inversor debe concentrar su diligencia.</t>
+  </si>
+  <si>
+    <t>4. La 'Compresión de P/E a 15x' suele ser el factor dominante porque actúa sobre el multiplicador entero del precio.</t>
+  </si>
+  <si>
+    <t>5. NOTA: Los escenarios son independientes. En un evento de mercado real, múltiples factores se correlacionan y amplifican.</t>
+  </si>
+  <si>
+    <t>Ticker</t>
+  </si>
+  <si>
     <t>Precio</t>
   </si>
   <si>
-    <t>Ratio P/E</t>
+    <t>P/E</t>
   </si>
   <si>
     <t>Beta</t>
-  </si>
-  <si>
-    <t>TICKER</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0\x"/>
     <numFmt numFmtId="166" formatCode="0.0%;\(0.0%\);\-"/>
-    <numFmt numFmtId="167" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="169" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\)"/>
+    <numFmt numFmtId="170" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -387,8 +644,82 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color rgb="FFE040FB"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFE040FB"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF64B5F6"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFFD54F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FFFFD54F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF7043"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFBDBDBD"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF66BB6A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFEF5350"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="24">
+  <fills count="27">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -458,7 +789,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF26A69A"/>
-        <bgColor rgb="FF008080"/>
+        <bgColor rgb="FF4F81BD"/>
       </patternFill>
     </fill>
     <fill>
@@ -527,8 +858,26 @@
         <bgColor rgb="FF1E1E2E"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF37474F"/>
+        <bgColor rgb="FF444466"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4A148C"/>
+        <bgColor rgb="FF1A237E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF12122A"/>
+        <bgColor rgb="FF1A1A2E"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -536,13 +885,80 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF444466"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF444466"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF444466"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF444466"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF444466"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF444466"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF444466"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -620,6 +1036,9 @@
     <xf numFmtId="166" fontId="9" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -656,49 +1075,131 @@
     <xf numFmtId="0" fontId="16" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="20" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="20" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="20" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="24" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="25" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="13" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="13" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="21" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="22" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="21" fillId="24" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="22" fillId="24" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="21" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="22" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="25" fillId="23" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="23" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="23" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="28" fillId="23" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="23" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="25" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="28" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -709,6 +1210,50 @@
     <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -721,7 +1266,7 @@
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="167" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="170" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -731,33 +1276,33 @@
       <rgbColor rgb="FFFFFFFF"/>
       <rgbColor rgb="FFFF0000"/>
       <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF303F9F"/>
       <rgbColor rgb="FFFFFF00"/>
       <rgbColor rgb="FFE040FB"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF6A1515"/>
       <rgbColor rgb="FF2E7D32"/>
-      <rgbColor rgb="FF1A1A2E"/>
+      <rgbColor rgb="FF12122A"/>
       <rgbColor rgb="FF558B2F"/>
-      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF303050"/>
       <rgbColor rgb="FF1B5E20"/>
-      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FFBDBDBD"/>
       <rgbColor rgb="FF757575"/>
       <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FFEF5350"/>
+      <rgbColor rgb="FF444466"/>
       <rgbColor rgb="FFEEEEEE"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF303050"/>
+      <rgbColor rgb="FF4A148C"/>
       <rgbColor rgb="FFFF8A80"/>
       <rgbColor rgb="FF1565C0"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF303F9F"/>
+      <rgbColor rgb="FFD9D9D9"/>
+      <rgbColor rgb="FF1A1A2E"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
       <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF37474F"/>
       <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF3949AB"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
@@ -765,22 +1310,22 @@
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF80CBC4"/>
       <rgbColor rgb="FFFF8A65"/>
-      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFB3B3B3"/>
       <rgbColor rgb="FFFFD54F"/>
-      <rgbColor rgb="FF3949AB"/>
+      <rgbColor rgb="FF3F51B5"/>
       <rgbColor rgb="FF64B5F6"/>
       <rgbColor rgb="FF66BB6A"/>
-      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF7043"/>
       <rgbColor rgb="FFFFA726"/>
       <rgbColor rgb="FFF57F17"/>
-      <rgbColor rgb="FF3F51B5"/>
+      <rgbColor rgb="FF4F81BD"/>
       <rgbColor rgb="FF9E9E9E"/>
       <rgbColor rgb="FF1A237E"/>
       <rgbColor rgb="FF26A69A"/>
       <rgbColor rgb="FF1E1E2E"/>
       <rgbColor rgb="FF212121"/>
       <rgbColor rgb="FFB71C1C"/>
-      <rgbColor rgb="FFFF7043"/>
+      <rgbColor rgb="FFEF5350"/>
       <rgbColor rgb="FF283593"/>
       <rgbColor rgb="FF2D2D44"/>
       <rgbColor rgb="00003366"/>
@@ -802,6 +1347,1105 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <c:style val="2"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1800" b="1" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-419" sz="1800" b="1" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>Distribución Monte Carlo — Fair Value COST (2,000 sims)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Frecuencia</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4F81BD"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-419"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Monte Carlo'!$A$24:$A$44</c:f>
+              <c:strCache>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>$169</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>$217</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>$264</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>$312</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>$359</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>$407</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>$454</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>$502</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>$549</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>$597</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>$644</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>$692</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>$739</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>$787</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>$834</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>$882</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>$929</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>$977</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>$1024</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>$1072</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>$1119</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Monte Carlo'!$B$24:$B$44</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>103</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>157</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>229</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>245</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>283</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>261</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>212</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F81E-4F2D-A366-1E318BD19B73}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="78838962"/>
+        <c:axId val="29032990"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="78838962"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" strike="noStrike" spc="-1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-419" sz="1000" b="1" strike="noStrike" spc="-1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:t>Fair Value ($)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="B3B3B3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-419"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="29032990"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="29032990"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="B3B3B3"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" strike="noStrike" spc="-1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-419" sz="1000" b="1" strike="noStrike" spc="-1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:t>Frecuencia</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="#,##0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="B3B3B3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-419"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="78838962"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-419"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <c:style val="2"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1800" b="1" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-419" sz="1800" b="1" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>Tornado — </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="el-GR" sz="1800" b="1" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>Δ </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="es-419" sz="1800" b="1" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>Fair Value vs Base ($780)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Tornado — Cisnes Negros'!$E$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Δ Bajo</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="EF5350"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-419"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Tornado — Cisnes Negros'!$A$4:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Disrupción Membresías (−80% Op.Income)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>P/E Compresión a 15x (Retail)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Crisis Kirkland (−40% EPS)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Bloqueo Pacífico (−25% Revenue)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Entrada Amazon (−15% Market Share)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Compresión P/E moderada (35x)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Shock de Tasa +5% (Pánico Fed)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Tornado — Cisnes Negros'!$E$4:$E$10</c:f>
+              <c:numCache>
+                <c:formatCode>\$#,##0.00;"($"#,##0.00\)</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>-670.8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-546</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-312</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-312</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-223.08</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-234.32759999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-2.3400000000000301</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DCE8-4622-B821-5F40C774C924}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Tornado — Cisnes Negros'!$F$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Δ Alto</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="66BB6A"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-419"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Tornado — Cisnes Negros'!$A$4:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Disrupción Membresías (−80% Op.Income)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>P/E Compresión a 15x (Retail)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Crisis Kirkland (−40% EPS)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Bloqueo Pacífico (−25% Revenue)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Entrada Amazon (−15% Market Share)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Compresión P/E moderada (35x)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Shock de Tasa +5% (Pánico Fed)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Tornado — Cisnes Negros'!$F$4:$F$10</c:f>
+              <c:numCache>
+                <c:formatCode>\$#,##0.00</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>156</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>62.4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>23.400000000000102</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.23399999999992399</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-DCE8-4622-B821-5F40C774C924}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="18398648"/>
+        <c:axId val="99920468"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="18398648"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" strike="noStrike" spc="-1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="el-GR" sz="1000" b="1" strike="noStrike" spc="-1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:t>Δ </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="es-419" sz="1000" b="1" strike="noStrike" spc="-1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:t>Fair Value ($)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="B3B3B3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-419"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="99920468"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="99920468"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="B3B3B3"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" strike="noStrike" spc="-1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-419" sz="1000" b="1" strike="noStrike" spc="-1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:t>Factor de Riesgo</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="B3B3B3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-419"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="18398648"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-419"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>211680</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>134280</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>322560</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>54360</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
@@ -931,31 +2575,34 @@
     <v>1987</v>
     <v>1005.82</v>
     <v>0.90939999999999999</v>
-    <v>-10.955</v>
-    <v>-1.0860000000000002E-2</v>
-    <v>442691992337</v>
+    <v>-9.32</v>
+    <v>-1.7210000000000001E-3</v>
+    <v>-9.2390000000000007E-3</v>
+    <v>-1.72</v>
+    <v>443417364175</v>
     <v>1008.79</v>
     <v>Costco Wholesale Corporation (Costco) opera almacenes de membresía y sitios de comercio electrónico que ofrecen una selección de productos de marca nacional y de marca privada en una amplia gama de categorías. La Compañía compra la mayoría de sus mercancías directamente a los proveedores y la dirige a puntos de consolidación de cross-docking (depósitos) o directamente a sus almacenes. Opera 891 almacenes, incluyendo 614 en los Estados Unidos y Puerto Rico, 108 en Canadá, 40 en México, 35 en Japón, 29 en el Reino Unido, 19 en Corea, 15 en Australia, 14 en Taiwán, siete en China, y más. cinco en España, dos en Francia, y uno en Islandia, Nueva Zelanda y Suecia. También opera sitios de comercio electrónico en los Estados Unidos, Canadá, el Reino Unido, México, Corea, Taiwán, Japón y Australia. La Compañía ofrece una amplia selección de mercancías, además de la conveniencia de departamentos especializados y servicios exclusivos para miembros.</v>
     <v>341000</v>
     <v>XNAS</v>
-    <v>46153.627683113278</v>
+    <v>46153.850181238282</v>
     <v>Nasdaq Stock Market</v>
     <v>0</v>
     <v>1007</v>
     <v>1067.08</v>
-    <v>995.02</v>
+    <v>985.15</v>
     <v>844.06</v>
     <v>USD</v>
     <v>COSTCO WHOLESALE CORPORATION</v>
     <v>COSTCO WHOLESALE CORPORATION</v>
-    <v>51.894399999999997</v>
-    <v>997.83500000000004</v>
+    <v>51.979399999999998</v>
+    <v>999.47</v>
+    <v>997.75</v>
     <v>Diversified Retail</v>
     <v>999 Lake Dr, ISSAQUAH, WA, 98027- US</v>
     <v>COST</v>
     <v>Acciones</v>
     <v>COSTCO WHOLESALE CORPORATION (XNAS:COST)</v>
-    <v>406806</v>
+    <v>2049558</v>
     <v>1785965</v>
   </rv>
   <rv s="2">
@@ -989,7 +2636,9 @@
     <k n="Apertura"/>
     <k n="Beta"/>
     <k n="Cambio"/>
+    <k n="Cambio % (horario ampliado)"/>
     <k n="Cambio (%)"/>
+    <k n="Cambio (horario ampliado)"/>
     <k n="Capitalización de mercado"/>
     <k n="Cierre anterior"/>
     <k n="Descripción" t="s"/>
@@ -1007,6 +2656,7 @@
     <k n="Nombre oficial" t="s"/>
     <k n="P/I"/>
     <k n="Precio"/>
+    <k n="Precio (horario ampliado)"/>
     <k n="Sector" t="s"/>
     <k n="Sede central" t="s"/>
     <k n="Símbolo bursátil" t="s"/>
@@ -1024,7 +2674,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="1">
-    <a count="43">
+    <a count="46">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -1036,13 +2686,16 @@
       <v t="s">Nombre</v>
       <v t="s">_SubLabel</v>
       <v t="s">Precio</v>
+      <v t="s">Precio (horario ampliado)</v>
       <v t="s">Intercambio</v>
       <v t="s">Nombre oficial</v>
       <v t="s">Hora de la última operación</v>
       <v t="s">Símbolo bursátil</v>
       <v t="s">Abreviatura de intercambio</v>
       <v t="s">Cambio</v>
+      <v t="s">Cambio (horario ampliado)</v>
       <v t="s">Cambio (%)</v>
+      <v t="s">Cambio % (horario ampliado)</v>
       <v t="s">Moneda</v>
       <v t="s">Cierre anterior</v>
       <v t="s">Apertura</v>
@@ -1101,8 +2754,11 @@
       <v>52 week high</v>
       <v>52 week low</v>
       <v>Shares outstanding</v>
+      <v>Change (Extended hours)</v>
       <v>Market cap</v>
+      <v>Price (Extended hours)</v>
       <v>Exchange abbreviation</v>
+      <v>Change % (Extended hours)</v>
       <v>Last trade time</v>
     </spb>
     <spb s="1">
@@ -1140,14 +2796,20 @@
       <v>2</v>
       <v>2</v>
       <v>4</v>
+      <v>2</v>
       <v>8</v>
+      <v>2</v>
+      <v>5</v>
       <v>9</v>
     </spb>
     <spb s="5">
       <v xml:space="preserve">desde el cierre anterior </v>
-      <v>Tiempo real Nasdaq Última venta</v>
+      <v xml:space="preserve">al cierre </v>
       <v xml:space="preserve">desde el cierre anterior </v>
       <v>Origen: Nasdaq Última venta</v>
+      <v xml:space="preserve">desde el cierre </v>
+      <v>Tiempo real Nasdaq Última venta</v>
+      <v xml:space="preserve">desde el cierre </v>
       <v>GMT</v>
     </spb>
   </spbData>
@@ -1186,8 +2848,11 @@
     <k n="Máximo en 52 semanas" t="s"/>
     <k n="Mínimo en 52 semanas" t="s"/>
     <k n="Acciones en circulación" t="s"/>
+    <k n="Cambio (horario ampliado)" t="s"/>
     <k n="Capitalización de mercado" t="s"/>
+    <k n="Precio (horario ampliado)" t="s"/>
     <k n="Abreviatura de intercambio" t="s"/>
+    <k n="Cambio % (horario ampliado)" t="s"/>
     <k n="Hora de la última operación" t="s"/>
   </s>
   <s>
@@ -1225,7 +2890,10 @@
     <k n="Máximo en 52 semanas" t="i"/>
     <k n="Mínimo en 52 semanas" t="i"/>
     <k n="Acciones en circulación" t="i"/>
+    <k n="Cambio (horario ampliado)" t="i"/>
     <k n="Capitalización de mercado" t="i"/>
+    <k n="Precio (horario ampliado)" t="i"/>
+    <k n="Cambio % (horario ampliado)" t="i"/>
     <k n="Hora de la última operación" t="i"/>
   </s>
   <s>
@@ -1233,6 +2901,9 @@
     <k n="Precio" t="s"/>
     <k n="Cambio (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
+    <k n="Cambio (horario ampliado)" t="s"/>
+    <k n="Precio (horario ampliado)" t="s"/>
+    <k n="Cambio % (horario ampliado)" t="s"/>
     <k n="Hora de la última operación" t="s"/>
   </s>
 </spbStructures>
@@ -1248,6 +2919,12 @@
       <x:numFmt numFmtId="0" formatCode="General"/>
     </x:dxf>
     <x:dxf>
+      <x:numFmt numFmtId="27" formatCode="d/m/yyyy\ hh:mm"/>
+    </x:dxf>
+    <x:dxf>
+      <x:numFmt numFmtId="14" formatCode="0.00%"/>
+    </x:dxf>
+    <x:dxf>
       <x:numFmt numFmtId="3" formatCode="#,##0"/>
     </x:dxf>
     <x:dxf>
@@ -1256,19 +2933,13 @@
     <x:dxf>
       <x:numFmt numFmtId="1" formatCode="0"/>
     </x:dxf>
-    <x:dxf>
-      <x:numFmt numFmtId="27" formatCode="d/m/yyyy\ hh:mm"/>
-    </x:dxf>
-    <x:dxf>
-      <x:numFmt numFmtId="14" formatCode="0.00%"/>
-    </x:dxf>
   </dxfs>
   <richProperties>
     <rPr n="NumberFormat" t="s"/>
     <rPr n="IsTitleField" t="b"/>
   </richProperties>
   <richStyles>
-    <rSty dxfid="3">
+    <rSty dxfid="5">
       <rpv i="0">#,##0.00</rpv>
     </rSty>
     <rSty dxfid="1">
@@ -1277,36 +2948,36 @@
     <rSty>
       <rpv i="1">1</rpv>
     </rSty>
-    <rSty dxfid="2">
+    <rSty dxfid="4">
       <rpv i="0">#,##0</rpv>
     </rSty>
-    <rSty dxfid="6"/>
+    <rSty dxfid="3"/>
     <rSty dxfid="0">
       <rpv i="0">0.00</rpv>
     </rSty>
-    <rSty dxfid="4">
+    <rSty dxfid="6">
       <rpv i="0">0</rpv>
     </rSty>
     <rSty dxfid="1">
       <rpv i="0">_([$$-en-US]* #,##0_);_([$$-en-US]* (#,##0);_([$$-en-US]* "-"_);_(@_)</rpv>
     </rSty>
-    <rSty dxfid="5"/>
+    <rSty dxfid="2"/>
   </richStyles>
 </richStyleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{661CF455-7585-495E-B04D-017157B7198B}" name="Tabla1" displayName="Tabla1" ref="I1:L2" totalsRowShown="0">
-  <autoFilter ref="I1:L2" xr:uid="{661CF455-7585-495E-B04D-017157B7198B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BDB7A695-0301-4C27-94B9-5CBC58DC4A48}" name="Tabla1" displayName="Tabla1" ref="I1:L2" totalsRowShown="0">
+  <autoFilter ref="I1:L2" xr:uid="{BDB7A695-0301-4C27-94B9-5CBC58DC4A48}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{452D659F-4C30-42A4-B9D7-75945FF3B957}" name="TICKER"/>
-    <tableColumn id="2" xr3:uid="{2018FA51-AED9-4715-B0CA-6FB8CEF08F1C}" name="Precio" dataDxfId="2">
+    <tableColumn id="1" xr3:uid="{F3EA13A3-C831-4DB4-BCE6-4A45E81C9711}" name="Ticker"/>
+    <tableColumn id="2" xr3:uid="{EDE7B658-91DF-43A0-B6AE-F44CC5962FCD}" name="Precio" dataDxfId="2">
       <calculatedColumnFormula array="1">_FV(I2,"Precio")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{53577388-E59D-46A4-B07B-7596EA3D4FFE}" name="Ratio P/E" dataDxfId="1">
+    <tableColumn id="3" xr3:uid="{470A2378-CB3A-4DFD-A00B-508588A527C0}" name="P/E" dataDxfId="1">
       <calculatedColumnFormula array="1">_FV(I2,"P/I",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{EDEDB454-D1B3-44E3-BDDD-E932B34E1477}" name="Beta" dataDxfId="0">
+    <tableColumn id="4" xr3:uid="{2CFFFEC1-1B22-4C45-86B7-4779917DC7BA}" name="Beta" dataDxfId="0">
       <calculatedColumnFormula array="1">_FV(I2,"Beta")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1501,613 +3172,610 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="16" customWidth="1"/>
+    <col min="2" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="30" customWidth="1"/>
     <col min="9" max="9" width="47.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
       <c r="I1" t="s">
-        <v>58</v>
+        <v>139</v>
       </c>
       <c r="J1" t="s">
-        <v>55</v>
+        <v>140</v>
       </c>
       <c r="K1" t="s">
-        <v>56</v>
+        <v>141</v>
       </c>
       <c r="L1" t="s">
-        <v>57</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
       <c r="I2" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="J2" s="39" cm="1">
+      <c r="J2" s="112" cm="1">
         <f t="array" aca="1" ref="J2" ca="1">_FV(I2,"Precio")</f>
-        <v>997.83500000000004</v>
-      </c>
-      <c r="K2" s="40" cm="1">
+        <v>999.47</v>
+      </c>
+      <c r="K2" s="113" cm="1">
         <f t="array" aca="1" ref="K2" ca="1">_FV(I2,"P/I",TRUE)</f>
-        <v>51.894399999999997</v>
-      </c>
-      <c r="L2" s="40" cm="1">
+        <v>51.979399999999998</v>
+      </c>
+      <c r="L2" s="113" cm="1">
         <f t="array" aca="1" ref="L2" ca="1">_FV(I2,"Beta")</f>
         <v>0.90939999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="43"/>
-      <c r="C3" s="44" t="s">
+      <c r="B3" s="12"/>
+      <c r="C3" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="44"/>
-      <c r="E3" s="45" t="s">
+      <c r="D3" s="11"/>
+      <c r="E3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
     </row>
     <row r="4" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="3" cm="1">
+      <c r="B4" s="16" cm="1">
         <f t="array" aca="1" ref="B4" ca="1">_FV(I2,"Precio")</f>
-        <v>997.83500000000004</v>
-      </c>
-      <c r="C4" s="2" t="s">
+        <v>999.47</v>
+      </c>
+      <c r="C4" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="4" cm="1">
+      <c r="D4" s="17" cm="1">
         <f t="array" aca="1" ref="D4" ca="1">_FV(I2,"P/I",TRUE)</f>
-        <v>51.894399999999997</v>
-      </c>
-      <c r="E4" s="5" t="s">
+        <v>51.979399999999998</v>
+      </c>
+      <c r="E4" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="46" t="s">
+      <c r="F4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="46"/>
+      <c r="G4" s="9"/>
     </row>
     <row r="5" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="47" t="s">
+      <c r="A5" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="47" t="s">
+      <c r="B5" s="8"/>
+      <c r="C5" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47" t="s">
+      <c r="D5" s="8"/>
+      <c r="E5" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="47"/>
-      <c r="G5" s="47"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
     </row>
     <row r="6" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="42" t="s">
+      <c r="A6" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="42"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
     </row>
     <row r="7" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="24" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="26">
         <f ca="1">($B$4/$D$4)*15*(1-0*0.06)</f>
-        <v>288.42273925510273</v>
-      </c>
-      <c r="C8" s="13">
+        <v>288.4229136927321</v>
+      </c>
+      <c r="C8" s="26">
         <f ca="1">($B$4/$D$4)*25*(1-0*0.06)</f>
-        <v>480.70456542517121</v>
-      </c>
-      <c r="D8" s="13">
+        <v>480.70485615455357</v>
+      </c>
+      <c r="D8" s="26">
         <f ca="1">($B$4/$D$4)*35*(1-0*0.06)</f>
-        <v>672.98639159523964</v>
-      </c>
-      <c r="E8" s="13">
+        <v>672.98679861637493</v>
+      </c>
+      <c r="E8" s="26">
         <f ca="1">($B$4/$D$4)*50*(1-0*0.06)</f>
-        <v>961.40913085034242</v>
-      </c>
-      <c r="F8" s="13">
+        <v>961.40971230910714</v>
+      </c>
+      <c r="F8" s="26">
         <f ca="1">($B$4/$D$4)*60*(1-0*0.06)</f>
-        <v>1153.6909570204109</v>
+        <v>1153.6916547709284</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="28">
         <f ca="1">($B$4/$D$4)*15*(1-0.005*0.06)</f>
-        <v>288.33621243332618</v>
-      </c>
-      <c r="C9" s="15">
+        <v>288.33638681862431</v>
+      </c>
+      <c r="C9" s="28">
         <f ca="1">($B$4/$D$4)*25*(1-0.005*0.06)</f>
-        <v>480.56035405554366</v>
-      </c>
-      <c r="D9" s="15">
+        <v>480.56064469770723</v>
+      </c>
+      <c r="D9" s="28">
         <f ca="1">($B$4/$D$4)*35*(1-0.005*0.06)</f>
-        <v>672.78449567776113</v>
-      </c>
-      <c r="E9" s="15">
+        <v>672.78490257679005</v>
+      </c>
+      <c r="E9" s="28">
         <f ca="1">($B$4/$D$4)*50*(1-0.005*0.06)</f>
-        <v>961.12070811108731</v>
-      </c>
-      <c r="F9" s="15">
+        <v>961.12128939541446</v>
+      </c>
+      <c r="F9" s="28">
         <f ca="1">($B$4/$D$4)*60*(1-0.005*0.06)</f>
-        <v>1153.3448497333047</v>
+        <v>1153.3455472744972</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="30">
         <f ca="1">($B$4/$D$4)*15*(1-0.01*0.06)</f>
-        <v>288.24968561154964</v>
-      </c>
-      <c r="C10" s="17">
+        <v>288.24985994451646</v>
+      </c>
+      <c r="C10" s="30">
         <f ca="1">($B$4/$D$4)*25*(1-0.01*0.06)</f>
-        <v>480.4161426859161</v>
-      </c>
-      <c r="D10" s="17">
+        <v>480.41643324086084</v>
+      </c>
+      <c r="D10" s="30">
         <f ca="1">($B$4/$D$4)*35*(1-0.01*0.06)</f>
-        <v>672.58259976028251</v>
-      </c>
-      <c r="E10" s="17">
+        <v>672.58300653720505</v>
+      </c>
+      <c r="E10" s="30">
         <f ca="1">($B$4/$D$4)*50*(1-0.01*0.06)</f>
-        <v>960.8322853718322</v>
-      </c>
-      <c r="F10" s="17">
+        <v>960.83286648172168</v>
+      </c>
+      <c r="F10" s="30">
         <f ca="1">($B$4/$D$4)*60*(1-0.01*0.06)</f>
-        <v>1152.9987424461985</v>
+        <v>1152.9994397780658</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="19">
+      <c r="B11" s="32">
         <f ca="1">($B$4/$D$4)*15*(1-0.025*0.06)</f>
-        <v>287.99010514622006</v>
-      </c>
-      <c r="C11" s="19">
+        <v>287.99027932219303</v>
+      </c>
+      <c r="C11" s="32">
         <f ca="1">($B$4/$D$4)*25*(1-0.025*0.06)</f>
-        <v>479.98350857703349</v>
-      </c>
-      <c r="D11" s="19">
+        <v>479.98379887032178</v>
+      </c>
+      <c r="D11" s="32">
         <f ca="1">($B$4/$D$4)*35*(1-0.025*0.06)</f>
-        <v>671.97691200784686</v>
-      </c>
-      <c r="E11" s="19">
+        <v>671.97731841845041</v>
+      </c>
+      <c r="E11" s="32">
         <f ca="1">($B$4/$D$4)*50*(1-0.025*0.06)</f>
-        <v>959.96701715406698</v>
-      </c>
-      <c r="F11" s="19">
+        <v>959.96759774064355</v>
+      </c>
+      <c r="F11" s="32">
         <f ca="1">($B$4/$D$4)*60*(1-0.025*0.06)</f>
-        <v>1151.9604205848802</v>
+        <v>1151.9611172887721</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="21">
+      <c r="B12" s="34">
         <f ca="1">($B$4/$D$4)*15*(1-0.05*0.06)</f>
-        <v>287.55747103733739</v>
-      </c>
-      <c r="C12" s="21">
+        <v>287.55764495165391</v>
+      </c>
+      <c r="C12" s="34">
         <f ca="1">($B$4/$D$4)*25*(1-0.05*0.06)</f>
-        <v>479.26245172889571</v>
-      </c>
-      <c r="D12" s="21">
+        <v>479.26274158608993</v>
+      </c>
+      <c r="D12" s="34">
         <f ca="1">($B$4/$D$4)*35*(1-0.05*0.06)</f>
-        <v>670.96743242045386</v>
-      </c>
-      <c r="E12" s="21">
+        <v>670.96783822052578</v>
+      </c>
+      <c r="E12" s="34">
         <f ca="1">($B$4/$D$4)*50*(1-0.05*0.06)</f>
-        <v>958.52490345779142</v>
-      </c>
-      <c r="F12" s="21">
+        <v>958.52548317217986</v>
+      </c>
+      <c r="F12" s="34">
         <f ca="1">($B$4/$D$4)*60*(1-0.05*0.06)</f>
-        <v>1150.2298841493496</v>
+        <v>1150.2305798066157</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="42" t="s">
+      <c r="A13" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="42"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="42"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
     </row>
     <row r="14" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="24" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="22">
+      <c r="B15" s="35">
         <f t="shared" ref="B15:F19" ca="1" si="0">(B8-$B$4)/$B$4</f>
-        <v>-0.71095147067891717</v>
-      </c>
-      <c r="C15" s="22">
+        <v>-0.71142414110205199</v>
+      </c>
+      <c r="C15" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.51825245113152851</v>
-      </c>
-      <c r="D15" s="22">
+        <v>-0.51904023517008657</v>
+      </c>
+      <c r="D15" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.32555343158414007</v>
-      </c>
-      <c r="E15" s="22">
+        <v>-0.32665632923812132</v>
+      </c>
+      <c r="E15" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>-3.650490226305713E-2</v>
-      </c>
-      <c r="F15" s="22">
+        <v>-3.8080470340173179E-2</v>
+      </c>
+      <c r="F15" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>0.15619411728433144</v>
+        <v>0.15430343559179199</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="23">
+      <c r="B16" s="36">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.71103818523771345</v>
-      </c>
-      <c r="C16" s="23">
+        <v>-0.71151071385972131</v>
+      </c>
+      <c r="C16" s="36">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.51839697539618901</v>
-      </c>
-      <c r="D16" s="23">
+        <v>-0.51918452309953556</v>
+      </c>
+      <c r="D16" s="36">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.32575576555466473</v>
-      </c>
-      <c r="E16" s="23">
+        <v>-0.32685833233934986</v>
+      </c>
+      <c r="E16" s="36">
         <f t="shared" ca="1" si="0"/>
-        <v>-3.6793950792378224E-2</v>
-      </c>
-      <c r="F16" s="23">
+        <v>-3.8369046199071069E-2</v>
+      </c>
+      <c r="F16" s="36">
         <f t="shared" ca="1" si="0"/>
-        <v>0.15584725904914609</v>
+        <v>0.15395714456111459</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="16" t="s">
+      <c r="A17" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="24">
+      <c r="B17" s="37">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.71112489979650972</v>
-      </c>
-      <c r="C17" s="24">
+        <v>-0.71159728661739086</v>
+      </c>
+      <c r="C17" s="37">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.51854149966084961</v>
-      </c>
-      <c r="D17" s="24">
+        <v>-0.51932881102898443</v>
+      </c>
+      <c r="D17" s="37">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.32595809952518956</v>
-      </c>
-      <c r="E17" s="24">
+        <v>-0.3270603354405785</v>
+      </c>
+      <c r="E17" s="37">
         <f t="shared" ca="1" si="0"/>
-        <v>-3.7082999321699311E-2</v>
-      </c>
-      <c r="F17" s="24">
+        <v>-3.865762205796907E-2</v>
+      </c>
+      <c r="F17" s="37">
         <f t="shared" ca="1" si="0"/>
-        <v>0.15550040081396074</v>
+        <v>0.15361085353043694</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="25">
+      <c r="B18" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.71138504347289888</v>
-      </c>
-      <c r="C18" s="25">
+        <v>-0.71185700489039894</v>
+      </c>
+      <c r="C18" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.51897507245483121</v>
-      </c>
-      <c r="D18" s="25">
+        <v>-0.51976167481733138</v>
+      </c>
+      <c r="D18" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.32656510143676376</v>
-      </c>
-      <c r="E18" s="25">
+        <v>-0.32766634474426409</v>
+      </c>
+      <c r="E18" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>-3.7950144909662475E-2</v>
-      </c>
-      <c r="F18" s="25">
+        <v>-3.9523349634662842E-2</v>
+      </c>
+      <c r="F18" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>0.15445982610840489</v>
+        <v>0.15257198043840445</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="20" t="s">
+      <c r="A19" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="26">
+      <c r="B19" s="39">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.71181861626688048</v>
-      </c>
-      <c r="C19" s="26">
+        <v>-0.71228986867874589</v>
+      </c>
+      <c r="C19" s="39">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.51969769377813402</v>
-      </c>
-      <c r="D19" s="26">
+        <v>-0.52048311446457629</v>
+      </c>
+      <c r="D19" s="39">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.32757677128938767</v>
-      </c>
-      <c r="E19" s="26">
+        <v>-0.32867636025040697</v>
+      </c>
+      <c r="E19" s="39">
         <f t="shared" ca="1" si="0"/>
-        <v>-3.9395387556267931E-2</v>
-      </c>
-      <c r="F19" s="26">
+        <v>-4.0966228929152616E-2</v>
+      </c>
+      <c r="F19" s="39">
         <f t="shared" ca="1" si="0"/>
-        <v>0.15272553493247834</v>
+        <v>0.15084052528501668</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="48" t="s">
+      <c r="A20" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="48"/>
-      <c r="C20" s="48"/>
-      <c r="D20" s="48"/>
-      <c r="E20" s="48"/>
-      <c r="F20" s="48"/>
-      <c r="G20" s="48"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
     </row>
     <row r="21" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="42" t="s">
+      <c r="A21" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="42"/>
-      <c r="C21" s="42"/>
-      <c r="D21" s="42"/>
-      <c r="E21" s="42"/>
-      <c r="F21" s="42"/>
-      <c r="G21" s="42"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
     </row>
     <row r="22" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="C22" s="49" t="s">
+      <c r="C22" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D22" s="49"/>
-      <c r="E22" s="49"/>
-      <c r="F22" s="49"/>
-      <c r="G22" s="49"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
     </row>
     <row r="23" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="27" t="s">
+      <c r="A23" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="28" t="s">
+      <c r="B23" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="C23" s="50" t="s">
+      <c r="C23" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="50"/>
-      <c r="E23" s="50"/>
-      <c r="F23" s="50"/>
-      <c r="G23" s="50"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
     </row>
     <row r="24" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="29" t="s">
+      <c r="A24" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="B24" s="30" t="s">
+      <c r="B24" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="C24" s="51" t="s">
+      <c r="C24" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="51"/>
-      <c r="E24" s="51"/>
-      <c r="F24" s="51"/>
-      <c r="G24" s="51"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
     </row>
     <row r="25" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="31" t="s">
+      <c r="A25" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="32" t="s">
+      <c r="B25" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="52" t="s">
+      <c r="C25" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D25" s="52"/>
-      <c r="E25" s="52"/>
-      <c r="F25" s="52"/>
-      <c r="G25" s="52"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
     </row>
     <row r="26" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="33" t="s">
+      <c r="A26" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="34" t="s">
+      <c r="B26" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="C26" s="53" t="s">
+      <c r="C26" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D26" s="53"/>
-      <c r="E26" s="53"/>
-      <c r="F26" s="53"/>
-      <c r="G26" s="53"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
     </row>
     <row r="27" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="35" t="s">
+      <c r="A27" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="B27" s="36" t="s">
+      <c r="B27" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="C27" s="54" t="s">
+      <c r="C27" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D27" s="54"/>
-      <c r="E27" s="54"/>
-      <c r="F27" s="54"/>
-      <c r="G27" s="54"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
     </row>
     <row r="28" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="42" t="s">
+      <c r="A28" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="B28" s="42"/>
-      <c r="C28" s="42"/>
-      <c r="D28" s="42"/>
-      <c r="E28" s="42"/>
-      <c r="F28" s="42"/>
-      <c r="G28" s="42"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
     </row>
     <row r="29" spans="1:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="37" t="s">
+      <c r="A29" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="B29" s="55" t="s">
+      <c r="B29" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="55"/>
-      <c r="D29" s="55"/>
-      <c r="E29" s="55"/>
-      <c r="F29" s="55"/>
-      <c r="G29" s="55"/>
+      <c r="C29" s="95"/>
+      <c r="D29" s="95"/>
+      <c r="E29" s="95"/>
+      <c r="F29" s="95"/>
+      <c r="G29" s="95"/>
     </row>
     <row r="30" spans="1:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="38" t="s">
+      <c r="A30" s="52" t="s">
         <v>48</v>
       </c>
-      <c r="B30" s="56" t="s">
+      <c r="B30" s="96" t="s">
         <v>49</v>
       </c>
-      <c r="C30" s="56"/>
-      <c r="D30" s="56"/>
-      <c r="E30" s="56"/>
-      <c r="F30" s="56"/>
-      <c r="G30" s="56"/>
+      <c r="C30" s="96"/>
+      <c r="D30" s="96"/>
+      <c r="E30" s="96"/>
+      <c r="F30" s="96"/>
+      <c r="G30" s="96"/>
     </row>
     <row r="31" spans="1:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="37" t="s">
+      <c r="A31" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="B31" s="55" t="s">
+      <c r="B31" s="95" t="s">
         <v>51</v>
       </c>
-      <c r="C31" s="55"/>
-      <c r="D31" s="55"/>
-      <c r="E31" s="55"/>
-      <c r="F31" s="55"/>
-      <c r="G31" s="55"/>
+      <c r="C31" s="95"/>
+      <c r="D31" s="95"/>
+      <c r="E31" s="95"/>
+      <c r="F31" s="95"/>
+      <c r="G31" s="95"/>
     </row>
     <row r="32" spans="1:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="38" t="s">
+      <c r="A32" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="B32" s="56" t="s">
+      <c r="B32" s="96" t="s">
         <v>53</v>
       </c>
-      <c r="C32" s="56"/>
-      <c r="D32" s="56"/>
-      <c r="E32" s="56"/>
-      <c r="F32" s="56"/>
-      <c r="G32" s="56"/>
+      <c r="C32" s="96"/>
+      <c r="D32" s="96"/>
+      <c r="E32" s="96"/>
+      <c r="F32" s="96"/>
+      <c r="G32" s="96"/>
     </row>
     <row r="33" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="57" t="s">
+      <c r="A33" s="97" t="s">
         <v>54</v>
       </c>
-      <c r="B33" s="57"/>
-      <c r="C33" s="57"/>
-      <c r="D33" s="57"/>
-      <c r="E33" s="57"/>
-      <c r="F33" s="57"/>
-      <c r="G33" s="57"/>
+      <c r="B33" s="97"/>
+      <c r="C33" s="97"/>
+      <c r="D33" s="97"/>
+      <c r="E33" s="97"/>
+      <c r="F33" s="97"/>
+      <c r="G33" s="97"/>
     </row>
     <row r="34" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2159,26 +3827,14 @@
     <mergeCell ref="E3:G3"/>
   </mergeCells>
   <conditionalFormatting sqref="B15:F19">
-    <cfRule type="colorScale" priority="1">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="num" val="0"/>
         <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B8:F12">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
+        <color rgb="FFB71C1C"/>
+        <color rgb="FFFFEB3B"/>
+        <color rgb="FF1B5E20"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
@@ -2188,4 +3844,957 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FF64B5F6"/>
+  </sheetPr>
+  <dimension ref="A1:J44"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="8" width="14" customWidth="1"/>
+    <col min="9" max="10" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="98" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="98"/>
+      <c r="H1" s="98"/>
+      <c r="I1" s="98"/>
+      <c r="J1" s="98"/>
+    </row>
+    <row r="2" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="99" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="99"/>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="99"/>
+    </row>
+    <row r="3" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="54">
+        <f ca="1">'Matriz de Sensibilidad'!B4</f>
+        <v>999.47</v>
+      </c>
+      <c r="C3" s="55" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="100" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="100"/>
+      <c r="F3" s="100"/>
+      <c r="G3" s="100"/>
+      <c r="H3" s="100"/>
+      <c r="I3" s="100"/>
+      <c r="J3" s="100"/>
+    </row>
+    <row r="4" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="53" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="56">
+        <f ca="1">'Matriz de Sensibilidad'!D4</f>
+        <v>51.979399999999998</v>
+      </c>
+      <c r="C4" s="55" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="100" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" s="100"/>
+      <c r="F4" s="100"/>
+      <c r="G4" s="100"/>
+      <c r="H4" s="100"/>
+      <c r="I4" s="100"/>
+      <c r="J4" s="100"/>
+    </row>
+    <row r="5" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="53" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" s="56">
+        <v>38</v>
+      </c>
+      <c r="C5" s="55" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" s="100" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="100"/>
+      <c r="F5" s="100"/>
+      <c r="G5" s="100"/>
+      <c r="H5" s="100"/>
+      <c r="I5" s="100"/>
+      <c r="J5" s="100"/>
+    </row>
+    <row r="6" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="53" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="57">
+        <v>9</v>
+      </c>
+      <c r="C6" s="55" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="100" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="100"/>
+      <c r="F6" s="100"/>
+      <c r="G6" s="100"/>
+      <c r="H6" s="100"/>
+      <c r="I6" s="100"/>
+      <c r="J6" s="100"/>
+    </row>
+    <row r="7" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="53" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="58">
+        <v>0.01</v>
+      </c>
+      <c r="C7" s="55" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7" s="100" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="100"/>
+      <c r="F7" s="100"/>
+      <c r="G7" s="100"/>
+      <c r="H7" s="100"/>
+      <c r="I7" s="100"/>
+      <c r="J7" s="100"/>
+    </row>
+    <row r="8" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="58">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="C8" s="55" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" s="100" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="100"/>
+      <c r="F8" s="100"/>
+      <c r="G8" s="100"/>
+      <c r="H8" s="100"/>
+      <c r="I8" s="100"/>
+      <c r="J8" s="100"/>
+    </row>
+    <row r="10" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="99" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" s="99"/>
+      <c r="C10" s="99"/>
+      <c r="D10" s="99"/>
+      <c r="E10" s="99"/>
+      <c r="F10" s="99"/>
+      <c r="G10" s="99"/>
+      <c r="H10" s="99"/>
+      <c r="I10" s="99"/>
+      <c r="J10" s="99"/>
+    </row>
+    <row r="11" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="59" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" s="59" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" s="101" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" s="101"/>
+      <c r="E11" s="101"/>
+      <c r="F11" s="101"/>
+      <c r="G11" s="101"/>
+      <c r="H11" s="101"/>
+      <c r="I11" s="101"/>
+      <c r="J11" s="101"/>
+    </row>
+    <row r="12" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="60" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="61">
+        <v>598.78095134615501</v>
+      </c>
+      <c r="C12" s="102" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="102"/>
+      <c r="E12" s="102"/>
+      <c r="F12" s="102"/>
+      <c r="G12" s="102"/>
+      <c r="H12" s="102"/>
+      <c r="I12" s="102"/>
+      <c r="J12" s="102"/>
+    </row>
+    <row r="13" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="62" t="s">
+        <v>76</v>
+      </c>
+      <c r="B13" s="63">
+        <v>598.70959401651498</v>
+      </c>
+      <c r="C13" s="103" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" s="103"/>
+      <c r="E13" s="103"/>
+      <c r="F13" s="103"/>
+      <c r="G13" s="103"/>
+      <c r="H13" s="103"/>
+      <c r="I13" s="103"/>
+      <c r="J13" s="103"/>
+    </row>
+    <row r="14" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="64" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" s="65">
+        <v>138.64326208939701</v>
+      </c>
+      <c r="C14" s="104" t="s">
+        <v>79</v>
+      </c>
+      <c r="D14" s="104"/>
+      <c r="E14" s="104"/>
+      <c r="F14" s="104"/>
+      <c r="G14" s="104"/>
+      <c r="H14" s="104"/>
+      <c r="I14" s="104"/>
+      <c r="J14" s="104"/>
+    </row>
+    <row r="15" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="66" t="s">
+        <v>80</v>
+      </c>
+      <c r="B15" s="67">
+        <v>373.023888775437</v>
+      </c>
+      <c r="C15" s="105" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" s="105"/>
+      <c r="E15" s="105"/>
+      <c r="F15" s="105"/>
+      <c r="G15" s="105"/>
+      <c r="H15" s="105"/>
+      <c r="I15" s="105"/>
+      <c r="J15" s="105"/>
+    </row>
+    <row r="16" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="68" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" s="69">
+        <v>505.28285927806701</v>
+      </c>
+      <c r="C16" s="106" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" s="106"/>
+      <c r="E16" s="106"/>
+      <c r="F16" s="106"/>
+      <c r="G16" s="106"/>
+      <c r="H16" s="106"/>
+      <c r="I16" s="106"/>
+      <c r="J16" s="106"/>
+    </row>
+    <row r="17" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="62" t="s">
+        <v>84</v>
+      </c>
+      <c r="B17" s="63">
+        <v>688.85409076321105</v>
+      </c>
+      <c r="C17" s="103" t="s">
+        <v>85</v>
+      </c>
+      <c r="D17" s="103"/>
+      <c r="E17" s="103"/>
+      <c r="F17" s="103"/>
+      <c r="G17" s="103"/>
+      <c r="H17" s="103"/>
+      <c r="I17" s="103"/>
+      <c r="J17" s="103"/>
+    </row>
+    <row r="18" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="66" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" s="67">
+        <v>829.16575850583104</v>
+      </c>
+      <c r="C18" s="105" t="s">
+        <v>87</v>
+      </c>
+      <c r="D18" s="105"/>
+      <c r="E18" s="105"/>
+      <c r="F18" s="105"/>
+      <c r="G18" s="105"/>
+      <c r="H18" s="105"/>
+      <c r="I18" s="105"/>
+      <c r="J18" s="105"/>
+    </row>
+    <row r="19" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="70" t="s">
+        <v>88</v>
+      </c>
+      <c r="B19" s="71">
+        <v>0.90149999999999997</v>
+      </c>
+      <c r="C19" s="107" t="s">
+        <v>89</v>
+      </c>
+      <c r="D19" s="107"/>
+      <c r="E19" s="107"/>
+      <c r="F19" s="107"/>
+      <c r="G19" s="107"/>
+      <c r="H19" s="107"/>
+      <c r="I19" s="107"/>
+      <c r="J19" s="107"/>
+    </row>
+    <row r="20" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="72" t="s">
+        <v>90</v>
+      </c>
+      <c r="B20" s="73">
+        <v>3.0499999999999999E-2</v>
+      </c>
+      <c r="C20" s="108" t="s">
+        <v>91</v>
+      </c>
+      <c r="D20" s="108"/>
+      <c r="E20" s="108"/>
+      <c r="F20" s="108"/>
+      <c r="G20" s="108"/>
+      <c r="H20" s="108"/>
+      <c r="I20" s="108"/>
+      <c r="J20" s="108"/>
+    </row>
+    <row r="22" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="99" t="s">
+        <v>92</v>
+      </c>
+      <c r="B22" s="99"/>
+      <c r="C22" s="99"/>
+      <c r="D22" s="99"/>
+      <c r="E22" s="99"/>
+      <c r="F22" s="99"/>
+      <c r="G22" s="99"/>
+      <c r="H22" s="99"/>
+      <c r="I22" s="99"/>
+      <c r="J22" s="99"/>
+    </row>
+    <row r="23" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="59" t="s">
+        <v>93</v>
+      </c>
+      <c r="B23" s="59" t="s">
+        <v>94</v>
+      </c>
+      <c r="C23" s="59" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="74" t="s">
+        <v>96</v>
+      </c>
+      <c r="B24" s="75">
+        <v>6</v>
+      </c>
+      <c r="C24" s="76">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="74" t="s">
+        <v>97</v>
+      </c>
+      <c r="B25" s="75">
+        <v>7</v>
+      </c>
+      <c r="C25" s="76">
+        <v>3.5000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="74" t="s">
+        <v>98</v>
+      </c>
+      <c r="B26" s="75">
+        <v>9</v>
+      </c>
+      <c r="C26" s="76">
+        <v>4.4999999999999997E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="74" t="s">
+        <v>99</v>
+      </c>
+      <c r="B27" s="75">
+        <v>31</v>
+      </c>
+      <c r="C27" s="76">
+        <v>1.55E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="B28" s="75">
+        <v>65</v>
+      </c>
+      <c r="C28" s="76">
+        <v>3.2500000000000001E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="74" t="s">
+        <v>101</v>
+      </c>
+      <c r="B29" s="75">
+        <v>103</v>
+      </c>
+      <c r="C29" s="76">
+        <v>5.1499999999999997E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="74" t="s">
+        <v>102</v>
+      </c>
+      <c r="B30" s="75">
+        <v>157</v>
+      </c>
+      <c r="C30" s="76">
+        <v>7.85E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="74" t="s">
+        <v>103</v>
+      </c>
+      <c r="B31" s="75">
+        <v>229</v>
+      </c>
+      <c r="C31" s="76">
+        <v>0.1145</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="74" t="s">
+        <v>104</v>
+      </c>
+      <c r="B32" s="75">
+        <v>245</v>
+      </c>
+      <c r="C32" s="76">
+        <v>0.1225</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="74" t="s">
+        <v>105</v>
+      </c>
+      <c r="B33" s="75">
+        <v>283</v>
+      </c>
+      <c r="C33" s="76">
+        <v>0.14149999999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="74" t="s">
+        <v>106</v>
+      </c>
+      <c r="B34" s="75">
+        <v>261</v>
+      </c>
+      <c r="C34" s="76">
+        <v>0.1305</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="77" t="s">
+        <v>107</v>
+      </c>
+      <c r="B35" s="78">
+        <v>212</v>
+      </c>
+      <c r="C35" s="79">
+        <v>0.106</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="77" t="s">
+        <v>108</v>
+      </c>
+      <c r="B36" s="78">
+        <v>160</v>
+      </c>
+      <c r="C36" s="79">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="77" t="s">
+        <v>109</v>
+      </c>
+      <c r="B37" s="78">
+        <v>97</v>
+      </c>
+      <c r="C37" s="79">
+        <v>4.8500000000000001E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="80" t="s">
+        <v>110</v>
+      </c>
+      <c r="B38" s="81">
+        <v>74</v>
+      </c>
+      <c r="C38" s="82">
+        <v>3.6999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="80" t="s">
+        <v>111</v>
+      </c>
+      <c r="B39" s="81">
+        <v>35</v>
+      </c>
+      <c r="C39" s="82">
+        <v>1.7500000000000002E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="80" t="s">
+        <v>112</v>
+      </c>
+      <c r="B40" s="81">
+        <v>16</v>
+      </c>
+      <c r="C40" s="82">
+        <v>8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="80" t="s">
+        <v>113</v>
+      </c>
+      <c r="B41" s="81">
+        <v>6</v>
+      </c>
+      <c r="C41" s="82">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="80" t="s">
+        <v>114</v>
+      </c>
+      <c r="B42" s="81">
+        <v>3</v>
+      </c>
+      <c r="C42" s="82">
+        <v>1.5E-3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="80" t="s">
+        <v>115</v>
+      </c>
+      <c r="B43" s="81">
+        <v>0</v>
+      </c>
+      <c r="C43" s="82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="80" t="s">
+        <v>116</v>
+      </c>
+      <c r="B44" s="81">
+        <v>1</v>
+      </c>
+      <c r="C44" s="82">
+        <v>5.0000000000000001E-4</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="C17:J17"/>
+    <mergeCell ref="C18:J18"/>
+    <mergeCell ref="C19:J19"/>
+    <mergeCell ref="C20:J20"/>
+    <mergeCell ref="A22:J22"/>
+    <mergeCell ref="C12:J12"/>
+    <mergeCell ref="C13:J13"/>
+    <mergeCell ref="C14:J14"/>
+    <mergeCell ref="C15:J15"/>
+    <mergeCell ref="C16:J16"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="A10:J10"/>
+    <mergeCell ref="C11:J11"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="D3:J3"/>
+    <mergeCell ref="D4:J4"/>
+    <mergeCell ref="D5:J5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FFEF5350"/>
+  </sheetPr>
+  <dimension ref="A1:H35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="36" customWidth="1"/>
+    <col min="2" max="5" width="16" customWidth="1"/>
+    <col min="6" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="98" t="s">
+        <v>117</v>
+      </c>
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="98"/>
+      <c r="H1" s="98"/>
+    </row>
+    <row r="2" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="109" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2" s="109"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="109"/>
+      <c r="E2" s="109"/>
+      <c r="F2" s="109"/>
+      <c r="G2" s="109"/>
+      <c r="H2" s="109"/>
+    </row>
+    <row r="3" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="59" t="s">
+        <v>119</v>
+      </c>
+      <c r="B3" s="59" t="s">
+        <v>120</v>
+      </c>
+      <c r="C3" s="59" t="s">
+        <v>121</v>
+      </c>
+      <c r="D3" s="59" t="s">
+        <v>122</v>
+      </c>
+      <c r="E3" s="59" t="s">
+        <v>123</v>
+      </c>
+      <c r="F3" s="59" t="s">
+        <v>124</v>
+      </c>
+      <c r="G3" s="59" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="83" t="s">
+        <v>126</v>
+      </c>
+      <c r="B4" s="84">
+        <v>109.2</v>
+      </c>
+      <c r="C4" s="85">
+        <v>780</v>
+      </c>
+      <c r="D4" s="86">
+        <v>819</v>
+      </c>
+      <c r="E4" s="87">
+        <v>-670.8</v>
+      </c>
+      <c r="F4" s="86">
+        <v>39</v>
+      </c>
+      <c r="G4" s="88">
+        <v>709.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="89" t="s">
+        <v>127</v>
+      </c>
+      <c r="B5" s="90">
+        <v>234</v>
+      </c>
+      <c r="C5" s="91">
+        <v>780</v>
+      </c>
+      <c r="D5" s="92">
+        <v>936</v>
+      </c>
+      <c r="E5" s="93">
+        <v>-546</v>
+      </c>
+      <c r="F5" s="92">
+        <v>156</v>
+      </c>
+      <c r="G5" s="94">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="83" t="s">
+        <v>128</v>
+      </c>
+      <c r="B6" s="84">
+        <v>468</v>
+      </c>
+      <c r="C6" s="85">
+        <v>780</v>
+      </c>
+      <c r="D6" s="86">
+        <v>858</v>
+      </c>
+      <c r="E6" s="87">
+        <v>-312</v>
+      </c>
+      <c r="F6" s="86">
+        <v>78</v>
+      </c>
+      <c r="G6" s="88">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="89" t="s">
+        <v>129</v>
+      </c>
+      <c r="B7" s="90">
+        <v>468</v>
+      </c>
+      <c r="C7" s="91">
+        <v>780</v>
+      </c>
+      <c r="D7" s="92">
+        <v>842.4</v>
+      </c>
+      <c r="E7" s="93">
+        <v>-312</v>
+      </c>
+      <c r="F7" s="92">
+        <v>62.4</v>
+      </c>
+      <c r="G7" s="94">
+        <v>374.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="83" t="s">
+        <v>130</v>
+      </c>
+      <c r="B8" s="84">
+        <v>556.91999999999996</v>
+      </c>
+      <c r="C8" s="85">
+        <v>780</v>
+      </c>
+      <c r="D8" s="86">
+        <v>803.4</v>
+      </c>
+      <c r="E8" s="87">
+        <v>-223.08</v>
+      </c>
+      <c r="F8" s="86">
+        <v>23.400000000000102</v>
+      </c>
+      <c r="G8" s="88">
+        <v>246.48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="89" t="s">
+        <v>131</v>
+      </c>
+      <c r="B9" s="90">
+        <v>545.67240000000004</v>
+      </c>
+      <c r="C9" s="91">
+        <v>780</v>
+      </c>
+      <c r="D9" s="92">
+        <v>780</v>
+      </c>
+      <c r="E9" s="93">
+        <v>-234.32759999999999</v>
+      </c>
+      <c r="F9" s="92">
+        <v>0</v>
+      </c>
+      <c r="G9" s="94">
+        <v>234.32759999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="83" t="s">
+        <v>132</v>
+      </c>
+      <c r="B10" s="84">
+        <v>777.66</v>
+      </c>
+      <c r="C10" s="85">
+        <v>780</v>
+      </c>
+      <c r="D10" s="86">
+        <v>780.23400000000004</v>
+      </c>
+      <c r="E10" s="87">
+        <v>-2.3400000000000301</v>
+      </c>
+      <c r="F10" s="86">
+        <v>0.23399999999992399</v>
+      </c>
+      <c r="G10" s="88">
+        <v>2.5739999999999599</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="99" t="s">
+        <v>133</v>
+      </c>
+      <c r="B30" s="99"/>
+      <c r="C30" s="99"/>
+      <c r="D30" s="99"/>
+      <c r="E30" s="99"/>
+      <c r="F30" s="99"/>
+      <c r="G30" s="99"/>
+      <c r="H30" s="99"/>
+    </row>
+    <row r="31" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="110" t="s">
+        <v>134</v>
+      </c>
+      <c r="B31" s="110"/>
+      <c r="C31" s="110"/>
+      <c r="D31" s="110"/>
+      <c r="E31" s="110"/>
+      <c r="F31" s="110"/>
+      <c r="G31" s="110"/>
+      <c r="H31" s="110"/>
+    </row>
+    <row r="32" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="111" t="s">
+        <v>135</v>
+      </c>
+      <c r="B32" s="111"/>
+      <c r="C32" s="111"/>
+      <c r="D32" s="111"/>
+      <c r="E32" s="111"/>
+      <c r="F32" s="111"/>
+      <c r="G32" s="111"/>
+      <c r="H32" s="111"/>
+    </row>
+    <row r="33" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="110" t="s">
+        <v>136</v>
+      </c>
+      <c r="B33" s="110"/>
+      <c r="C33" s="110"/>
+      <c r="D33" s="110"/>
+      <c r="E33" s="110"/>
+      <c r="F33" s="110"/>
+      <c r="G33" s="110"/>
+      <c r="H33" s="110"/>
+    </row>
+    <row r="34" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="111" t="s">
+        <v>137</v>
+      </c>
+      <c r="B34" s="111"/>
+      <c r="C34" s="111"/>
+      <c r="D34" s="111"/>
+      <c r="E34" s="111"/>
+      <c r="F34" s="111"/>
+      <c r="G34" s="111"/>
+      <c r="H34" s="111"/>
+    </row>
+    <row r="35" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="110" t="s">
+        <v>138</v>
+      </c>
+      <c r="B35" s="110"/>
+      <c r="C35" s="110"/>
+      <c r="D35" s="110"/>
+      <c r="E35" s="110"/>
+      <c r="F35" s="110"/>
+      <c r="G35" s="110"/>
+      <c r="H35" s="110"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A32:H32"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/Simulador_Riesgos_Costco_BlackSwan.xlsx
+++ b/Simulador_Riesgos_Costco_BlackSwan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luism\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32F193BB-87A0-4F7B-B9D0-FBA383A0CE77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55AC3C75-66B6-4C12-A6FD-E73FC14AB7F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Monte Carlo" sheetId="2" r:id="rId2"/>
     <sheet name="Tornado — Cisnes Negros" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="145">
   <si>
     <t>🦢  SIMULADOR DE RIESGOS COSTCO — Black Swan Edition</t>
   </si>
@@ -245,49 +245,49 @@
     <t>🎲  SIMULACIÓN MONTE CARLO — Distribución del Fair Value (COST)</t>
   </si>
   <si>
-    <t xml:space="preserve">  ⚙  PARÁMETROS DE SIMULACIÓN  (N = 2,000 iteraciones)</t>
+    <t xml:space="preserve">  ⚙  PARÁMETROS  |  Precio y P/E sincronizados con Hoja 1 (B4 y D4) — conecta allí tu fuente en tiempo real</t>
   </si>
   <si>
     <t>Precio Actual (COST)</t>
   </si>
   <si>
-    <t>← modifica</t>
-  </si>
-  <si>
-    <t>Precio spot May 2026. Source: Bloomberg, May 2026</t>
-  </si>
-  <si>
-    <t>P/E Actual</t>
-  </si>
-  <si>
-    <t>Consenso de mercado. Source: FactSet, May 2026</t>
-  </si>
-  <si>
-    <t>P/E Medio (μ)</t>
-  </si>
-  <si>
-    <t>Media histórica 5Y ajustada</t>
+    <t>🔗 Sincronizado con Hoja 1, B4 → conectar a Google Finance / cotización en tiempo real</t>
+  </si>
+  <si>
+    <t>P/E Actual (TTM)</t>
+  </si>
+  <si>
+    <t>🔗 Sincronizado con Hoja 1, D4 → conectar a Google Finance / cotización en tiempo real</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> = Precio ÷ P/E (calculado automático)</t>
+  </si>
+  <si>
+    <t>P/E Medio Simulación (μ)</t>
+  </si>
+  <si>
+    <t>✏️  Media histórica 5Y ajustada — modificable aquí</t>
   </si>
   <si>
     <t>P/E Desv. Estándar (σ)</t>
   </si>
   <si>
-    <t>Volatilidad implícita del múltiplo</t>
+    <t>✏️  Volatilidad del múltiplo — modificable aquí</t>
   </si>
   <si>
     <t>Shock Tasa Medio (μ)</t>
   </si>
   <si>
-    <t>Escenario base Fed +100bps</t>
+    <t>✏️  Escenario base Fed — modificable aquí</t>
   </si>
   <si>
     <t>Shock Tasa Desv. (σ)</t>
   </si>
   <si>
-    <t>Dispersión de escenarios macro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  📊  RESULTADOS ESTADÍSTICOS  (Fair Value Simulado)</t>
+    <t>✏️  Dispersión macro — modificable aquí</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  📊  RESULTADOS ESTADÍSTICOS  (N=2,000 — EPS sincronizado con Hoja 1)</t>
   </si>
   <si>
     <t>Métrica</t>
@@ -317,10 +317,10 @@
     <t>Dispersión de posibles Fair Values. Mayor σ = mayor incertidumbre.</t>
   </si>
   <si>
-    <t>Percentil 5% (Worst Case)</t>
-  </si>
-  <si>
-    <t>Solo el 5% de escenarios dan un precio menor. Proxy de 'tail risk'.</t>
+    <t>Percentil 5% — Worst Case</t>
+  </si>
+  <si>
+    <t>Solo el 5% de escenarios producen un precio menor. Proxy de tail risk.</t>
   </si>
   <si>
     <t>Percentil 25%</t>
@@ -335,25 +335,28 @@
     <t>Cuartil superior — escenario optimista moderado.</t>
   </si>
   <si>
-    <t>Percentil 95% (Best Case)</t>
+    <t>Percentil 95% — Best Case</t>
   </si>
   <si>
     <t>Solo el 5% de escenarios superan este precio.</t>
   </si>
   <si>
-    <t>Probabilidad de Pérdida vs $780</t>
-  </si>
-  <si>
-    <t>% de escenarios donde Fair Value &lt; Precio Actual.</t>
-  </si>
-  <si>
-    <t>Probabilidad Upside &gt;10%</t>
-  </si>
-  <si>
-    <t>% de escenarios donde Fair Value &gt; $858 (+10%).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  📈  HISTOGRAMA DE DISTRIBUCIÓN  (Fair Value Simulado — 2,000 iteraciones)</t>
+    <t>Prob. Pérdida vs Precio Actual</t>
+  </si>
+  <si>
+    <t>% simulaciones con Fair Value &lt; Precio Actual (Hoja 1, B4)</t>
+  </si>
+  <si>
+    <t>Prob. Upside &gt;10%</t>
+  </si>
+  <si>
+    <t>% simulaciones con Fair Value &gt; Precio Actual × 1.10</t>
+  </si>
+  <si>
+    <t>ℹ️  Al cambiar Precio o P/E en Hoja 1 (o cuando se actualicen en tiempo real), el EPS implícito cambia automáticamente. Los percentiles son la distribución actual — para recalibrar la simulación completa, actualiza los parámetros μ/σ arriba.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  📈  HISTOGRAMA DE DISTRIBUCIÓN  (2,000 iteraciones)</t>
   </si>
   <si>
     <t>Rango Fair Value</t>
@@ -365,73 +368,73 @@
     <t>Frecuencia (%)</t>
   </si>
   <si>
-    <t>$169</t>
-  </si>
-  <si>
-    <t>$217</t>
-  </si>
-  <si>
-    <t>$264</t>
-  </si>
-  <si>
-    <t>$312</t>
-  </si>
-  <si>
-    <t>$359</t>
-  </si>
-  <si>
-    <t>$407</t>
-  </si>
-  <si>
-    <t>$454</t>
-  </si>
-  <si>
-    <t>$502</t>
-  </si>
-  <si>
-    <t>$549</t>
-  </si>
-  <si>
-    <t>$597</t>
-  </si>
-  <si>
-    <t>$644</t>
-  </si>
-  <si>
-    <t>$692</t>
-  </si>
-  <si>
-    <t>$739</t>
+    <t>$209</t>
+  </si>
+  <si>
+    <t>$267</t>
+  </si>
+  <si>
+    <t>$325</t>
+  </si>
+  <si>
+    <t>$382</t>
+  </si>
+  <si>
+    <t>$440</t>
+  </si>
+  <si>
+    <t>$498</t>
+  </si>
+  <si>
+    <t>$556</t>
+  </si>
+  <si>
+    <t>$614</t>
+  </si>
+  <si>
+    <t>$671</t>
+  </si>
+  <si>
+    <t>$729</t>
   </si>
   <si>
     <t>$787</t>
   </si>
   <si>
-    <t>$834</t>
-  </si>
-  <si>
-    <t>$882</t>
-  </si>
-  <si>
-    <t>$929</t>
-  </si>
-  <si>
-    <t>$977</t>
-  </si>
-  <si>
-    <t>$1024</t>
-  </si>
-  <si>
-    <t>$1072</t>
-  </si>
-  <si>
-    <t>$1119</t>
+    <t>$845</t>
+  </si>
+  <si>
+    <t>$903</t>
+  </si>
+  <si>
+    <t>$960</t>
+  </si>
+  <si>
+    <t>$1018</t>
+  </si>
+  <si>
+    <t>$1076</t>
+  </si>
+  <si>
+    <t>$1134</t>
+  </si>
+  <si>
+    <t>$1192</t>
+  </si>
+  <si>
+    <t>$1249</t>
+  </si>
+  <si>
+    <t>$1307</t>
+  </si>
+  <si>
+    <t>$1365</t>
   </si>
   <si>
     <t>🌪  TORNADO — Impacto de Cisnes Negros en Fair Value (COST)</t>
   </si>
   <si>
-    <t xml:space="preserve">  Sensibilidad del Fair Value ante cada factor de riesgo — Base: $780 (P/E 50x, tasa base)</t>
+    <t xml:space="preserve">  Precio base y EPS sincronizados con Hoja 1 (B4 / D4) — se actualizan con la cotización en tiempo real</t>
   </si>
   <si>
     <t>Factor de Riesgo</t>
@@ -440,58 +443,61 @@
     <t>FV Pesimista</t>
   </si>
   <si>
-    <t>FV Base</t>
+    <t>FV Base (actual)</t>
   </si>
   <si>
     <t>FV Optimista</t>
   </si>
   <si>
-    <t>Δ Bajo</t>
-  </si>
-  <si>
-    <t>Δ Alto</t>
-  </si>
-  <si>
-    <t>Rango Total</t>
-  </si>
-  <si>
-    <t>Disrupción Membresías (−80% Op.Income)</t>
-  </si>
-  <si>
-    <t>P/E Compresión a 15x (Retail)</t>
-  </si>
-  <si>
-    <t>Crisis Kirkland (−40% EPS)</t>
-  </si>
-  <si>
-    <t>Bloqueo Pacífico (−25% Revenue)</t>
-  </si>
-  <si>
-    <t>Entrada Amazon (−15% Market Share)</t>
-  </si>
-  <si>
-    <t>Compresión P/E moderada (35x)</t>
-  </si>
-  <si>
-    <t>Shock de Tasa +5% (Pánico Fed)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  🔍  LECTURA DEL GRÁFICO TORNADO</t>
-  </si>
-  <si>
-    <t>1. Las barras ROJAS muestran el impacto negativo máximo de cada cisne negro en el Fair Value vs. el precio base de $780.</t>
-  </si>
-  <si>
-    <t>2. Las barras VERDES muestran el upside máximo si el factor se resuelve favorablemente.</t>
-  </si>
-  <si>
-    <t>3. El factor con la barra MÁS LARGA es el mayor driver de riesgo — donde el inversor debe concentrar su diligencia.</t>
-  </si>
-  <si>
-    <t>4. La 'Compresión de P/E a 15x' suele ser el factor dominante porque actúa sobre el multiplicador entero del precio.</t>
-  </si>
-  <si>
-    <t>5. NOTA: Los escenarios son independientes. En un evento de mercado real, múltiples factores se correlacionan y amplifican.</t>
+    <t>Δ Bajo ($)</t>
+  </si>
+  <si>
+    <t>Δ Alto ($)</t>
+  </si>
+  <si>
+    <t>Rango Total ($)</t>
+  </si>
+  <si>
+    <t>% Impacto</t>
+  </si>
+  <si>
+    <t>P/E Compresión a 15x (Reclasif. Retail)</t>
+  </si>
+  <si>
+    <t>Shock de Tasa +5% — Pánico Fed</t>
+  </si>
+  <si>
+    <t>Crisis Kirkland Signature (−40% EPS)</t>
+  </si>
+  <si>
+    <t>Disrupción Membresías (−80% Op. Income)</t>
+  </si>
+  <si>
+    <t>Bloqueo del Pacífico (−25% Revenue)</t>
+  </si>
+  <si>
+    <t>Entrada Amazon/Alibaba (−15% Mkt Share)</t>
+  </si>
+  <si>
+    <t>Compresión P/E moderada (35x, +1% Tasa)</t>
+  </si>
+  <si>
+    <t>[Rango auxiliar para gráfico — no modificar]</t>
+  </si>
+  <si>
+    <t>P/E Compresión a 15x (Reclasif. Retail</t>
+  </si>
+  <si>
+    <t>Disrupción Membresías (−80% Op. Income</t>
+  </si>
+  <si>
+    <t>Entrada Amazon/Alibaba (−15% Mkt Share</t>
+  </si>
+  <si>
+    <t>Compresión P/E moderada (35x, +1% Tasa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  🔍  LECTURA — Todos los valores se recalculan automáticamente cuando cambia B4 o D4 en Hoja 1.</t>
   </si>
   <si>
     <t>Ticker</t>
@@ -500,7 +506,7 @@
     <t>Precio</t>
   </si>
   <si>
-    <t>P/E</t>
+    <t>Ratio P/E</t>
   </si>
   <si>
     <t>Beta</t>
@@ -510,16 +516,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="7">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0\x"/>
     <numFmt numFmtId="166" formatCode="0.0%;\(0.0%\);\-"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\)"/>
-    <numFmt numFmtId="170" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="0.00\x"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="169" formatCode="0.0%"/>
+    <numFmt numFmtId="170" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\)"/>
+    <numFmt numFmtId="171" formatCode="0.0%;\(0.0%\)"/>
+    <numFmt numFmtId="172" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="34" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -666,6 +674,20 @@
       <family val="2"/>
     </font>
     <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF9E9E9E"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFD54F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
@@ -699,6 +721,7 @@
       <family val="2"/>
     </font>
     <font>
+      <b/>
       <sz val="10"/>
       <color rgb="FFBDBDBD"/>
       <name val="Calibri"/>
@@ -718,8 +741,28 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <i/>
+      <sz val="8"/>
+      <color rgb="FF555555"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF777777"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFE040FB"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="27">
+  <fills count="28">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -741,7 +784,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1565C0"/>
-        <bgColor rgb="FF3F51B5"/>
+        <bgColor rgb="FF0D47A1"/>
       </patternFill>
     </fill>
     <fill>
@@ -872,7 +915,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF12122A"/>
+        <fgColor rgb="FF0D47A1"/>
+        <bgColor rgb="FF303F9F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF111111"/>
         <bgColor rgb="FF1A1A2E"/>
       </patternFill>
     </fill>
@@ -917,7 +966,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="156">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1075,22 +1124,24 @@
     <xf numFmtId="0" fontId="16" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="20" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="20" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="20" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="20" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="22" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="22" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1129,78 +1180,182 @@
     <xf numFmtId="0" fontId="3" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="13" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="13" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="13" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="21" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="22" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="21" fillId="24" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="22" fillId="24" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="21" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="22" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="13" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="23" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="23" fillId="24" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="23" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="23" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="23" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="23" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="28" fillId="23" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="23" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="27" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="30" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="11" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="27" fillId="25" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="25" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="25" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="30" fillId="25" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="25" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="11" fillId="25" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="30" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="11" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="24" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="24" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="24" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="30" fillId="24" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="24" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="11" fillId="24" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="30" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="11" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="27" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="28" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="28" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="30" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="171" fontId="11" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="30" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="11" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1216,7 +1371,7 @@
     <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1243,16 +1398,28 @@
     <xf numFmtId="0" fontId="15" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="24" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="24" fillId="24" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="24" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="31" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1266,7 +1433,7 @@
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="170" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="172" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1274,7 +1441,7 @@
     <indexedColors>
       <rgbColor rgb="FF000000"/>
       <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FFEF5350"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF303F9F"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -1282,28 +1449,28 @@
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF6A1515"/>
       <rgbColor rgb="FF2E7D32"/>
-      <rgbColor rgb="FF12122A"/>
+      <rgbColor rgb="FF1A1A2E"/>
       <rgbColor rgb="FF558B2F"/>
       <rgbColor rgb="FF303050"/>
       <rgbColor rgb="FF1B5E20"/>
       <rgbColor rgb="FFBDBDBD"/>
-      <rgbColor rgb="FF757575"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF444466"/>
+      <rgbColor rgb="FF777777"/>
+      <rgbColor rgb="FF4F81BD"/>
+      <rgbColor rgb="FF555555"/>
       <rgbColor rgb="FFEEEEEE"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF4A148C"/>
       <rgbColor rgb="FFFF8A80"/>
       <rgbColor rgb="FF1565C0"/>
       <rgbColor rgb="FFD9D9D9"/>
-      <rgbColor rgb="FF1A1A2E"/>
+      <rgbColor rgb="FF111111"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF37474F"/>
       <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF0D47A1"/>
       <rgbColor rgb="FF3949AB"/>
-      <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FFCCFFCC"/>
@@ -1318,14 +1485,14 @@
       <rgbColor rgb="FFFF7043"/>
       <rgbColor rgb="FFFFA726"/>
       <rgbColor rgb="FFF57F17"/>
-      <rgbColor rgb="FF4F81BD"/>
+      <rgbColor rgb="FF757575"/>
       <rgbColor rgb="FF9E9E9E"/>
       <rgbColor rgb="FF1A237E"/>
       <rgbColor rgb="FF26A69A"/>
       <rgbColor rgb="FF1E1E2E"/>
       <rgbColor rgb="FF212121"/>
       <rgbColor rgb="FFB71C1C"/>
-      <rgbColor rgb="FFEF5350"/>
+      <rgbColor rgb="FF444466"/>
       <rgbColor rgb="FF283593"/>
       <rgbColor rgb="FF2D2D44"/>
       <rgbColor rgb="00003366"/>
@@ -1377,7 +1544,7 @@
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>Distribución Monte Carlo — Fair Value COST (2,000 sims)</a:t>
+              <a:t>Monte Carlo — Fair Value COST (EPS base: $19.05)</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1423,24 +1590,28 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:endParaRPr lang="es-419"/>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="outEnd"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
             <c:showBubbleSize val="1"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -1450,78 +1621,78 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Monte Carlo'!$A$24:$A$44</c:f>
+              <c:f>'Monte Carlo'!$A$25:$A$45</c:f>
               <c:strCache>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>$169</c:v>
+                  <c:v>$209</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>$217</c:v>
+                  <c:v>$267</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>$264</c:v>
+                  <c:v>$325</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>$312</c:v>
+                  <c:v>$382</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>$359</c:v>
+                  <c:v>$440</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>$407</c:v>
+                  <c:v>$498</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>$454</c:v>
+                  <c:v>$556</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>$502</c:v>
+                  <c:v>$614</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>$549</c:v>
+                  <c:v>$671</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>$597</c:v>
+                  <c:v>$729</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>$644</c:v>
+                  <c:v>$787</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>$692</c:v>
+                  <c:v>$845</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>$739</c:v>
+                  <c:v>$903</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>$787</c:v>
+                  <c:v>$960</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>$834</c:v>
+                  <c:v>$1018</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>$882</c:v>
+                  <c:v>$1076</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>$929</c:v>
+                  <c:v>$1134</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>$977</c:v>
+                  <c:v>$1192</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>$1024</c:v>
+                  <c:v>$1249</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>$1072</c:v>
+                  <c:v>$1307</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>$1119</c:v>
+                  <c:v>$1365</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Monte Carlo'!$B$24:$B$44</c:f>
+              <c:f>'Monte Carlo'!$B$25:$B$45</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="21"/>
@@ -1529,28 +1700,28 @@
                   <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>31</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>65</c:v>
+                  <c:v>66</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>103</c:v>
+                  <c:v>102</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>157</c:v>
+                  <c:v>156</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>229</c:v>
+                  <c:v>233</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>245</c:v>
+                  <c:v>241</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>283</c:v>
@@ -1559,25 +1730,25 @@
                   <c:v>261</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>212</c:v>
+                  <c:v>211</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>160</c:v>
+                  <c:v>161</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>97</c:v>
+                  <c:v>95</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>74</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>35</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>6</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>3</c:v>
@@ -1593,7 +1764,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-F81E-4F2D-A366-1E318BD19B73}"/>
+              <c16:uniqueId val="{00000000-2934-4C9B-A377-C9B71AC2ABC6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1606,11 +1777,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="78838962"/>
-        <c:axId val="29032990"/>
+        <c:axId val="96643978"/>
+        <c:axId val="85862296"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="78838962"/>
+        <c:axId val="96643978"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1650,7 +1821,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1676,7 +1847,7 @@
             <a:endParaRPr lang="es-419"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29032990"/>
+        <c:crossAx val="85862296"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1684,7 +1855,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="29032990"/>
+        <c:axId val="85862296"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1733,7 +1904,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="#,##0" sourceLinked="1"/>
+        <c:numFmt formatCode="#,##0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1759,7 +1930,7 @@
             <a:endParaRPr lang="es-419"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78838962"/>
+        <c:crossAx val="96643978"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1864,7 +2035,7 @@
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>Fair Value vs Base ($780)</a:t>
+              <a:t>Fair Value vs Precio Real (dinámico)</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1889,12 +2060,9 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Tornado — Cisnes Negros'!$E$3</c:f>
+              <c:f>'Tornado — Cisnes Negros'!$B$12</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Δ Bajo</c:v>
-                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
@@ -1918,24 +2086,28 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:endParaRPr lang="es-419"/>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="outEnd"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
             <c:showBubbleSize val="1"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -1945,66 +2117,66 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Tornado — Cisnes Negros'!$A$4:$A$10</c:f>
+              <c:f>'Tornado — Cisnes Negros'!$A$13:$A$19</c:f>
               <c:strCache>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>Disrupción Membresías (−80% Op.Income)</c:v>
+                  <c:v>P/E Compresión a 15x (Reclasif. Retail</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>P/E Compresión a 15x (Retail)</c:v>
+                  <c:v>Shock de Tasa +5% — Pánico Fed</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Crisis Kirkland (−40% EPS)</c:v>
+                  <c:v>Crisis Kirkland Signature (−40% EPS)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Bloqueo Pacífico (−25% Revenue)</c:v>
+                  <c:v>Disrupción Membresías (−80% Op. Income</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Entrada Amazon (−15% Market Share)</c:v>
+                  <c:v>Bloqueo del Pacífico (−25% Revenue)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Compresión P/E moderada (35x)</c:v>
+                  <c:v>Entrada Amazon/Alibaba (−15% Mkt Share</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>Shock de Tasa +5% (Pánico Fed)</c:v>
+                  <c:v>Compresión P/E moderada (35x, +1% Tasa</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Tornado — Cisnes Negros'!$E$4:$E$10</c:f>
+              <c:f>'Tornado — Cisnes Negros'!$B$13:$B$19</c:f>
               <c:numCache>
-                <c:formatCode>\$#,##0.00;"($"#,##0.00\)</c:formatCode>
+                <c:formatCode>\$#,##0.00</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>-670.8</c:v>
+                  <c:v>-713.7122833093805</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-546</c:v>
+                  <c:v>-2.9984100000000353</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-312</c:v>
+                  <c:v>-399.78800000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-312</c:v>
+                  <c:v>-866.11639887771094</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-223.08</c:v>
+                  <c:v>-427.95456661876096</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-234.32759999999999</c:v>
+                  <c:v>-319.36663427632561</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-2.3400000000000301</c:v>
+                  <c:v>-333.10205519192129</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-DCE8-4622-B821-5F40C774C924}"/>
+              <c16:uniqueId val="{00000000-EC29-4AD8-87BA-B245F37F6D94}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2013,12 +2185,9 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Tornado — Cisnes Negros'!$F$3</c:f>
+              <c:f>'Tornado — Cisnes Negros'!$C$12</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Δ Alto</c:v>
-                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
@@ -2042,24 +2211,28 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:endParaRPr lang="es-419"/>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="outEnd"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
             <c:showBubbleSize val="1"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -2069,66 +2242,66 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Tornado — Cisnes Negros'!$A$4:$A$10</c:f>
+              <c:f>'Tornado — Cisnes Negros'!$A$13:$A$19</c:f>
               <c:strCache>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>Disrupción Membresías (−80% Op.Income)</c:v>
+                  <c:v>P/E Compresión a 15x (Reclasif. Retail</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>P/E Compresión a 15x (Retail)</c:v>
+                  <c:v>Shock de Tasa +5% — Pánico Fed</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Crisis Kirkland (−40% EPS)</c:v>
+                  <c:v>Crisis Kirkland Signature (−40% EPS)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Bloqueo Pacífico (−25% Revenue)</c:v>
+                  <c:v>Disrupción Membresías (−80% Op. Income</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Entrada Amazon (−15% Market Share)</c:v>
+                  <c:v>Bloqueo del Pacífico (−25% Revenue)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Compresión P/E moderada (35x)</c:v>
+                  <c:v>Entrada Amazon/Alibaba (−15% Mkt Share</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>Shock de Tasa +5% (Pánico Fed)</c:v>
+                  <c:v>Compresión P/E moderada (35x, +1% Tasa</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Tornado — Cisnes Negros'!$F$4:$F$10</c:f>
+              <c:f>'Tornado — Cisnes Negros'!$C$13:$C$19</c:f>
               <c:numCache>
                 <c:formatCode>\$#,##0.00</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>39</c:v>
+                  <c:v>143.5608667624781</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>156</c:v>
+                  <c:v>0.2998410000000149</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>78</c:v>
+                  <c:v>99.947000000000116</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>62.4</c:v>
+                  <c:v>49.973500000000058</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>23.400000000000102</c:v>
+                  <c:v>79.957600000000184</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>29.984100000000126</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.23399999999992399</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-DCE8-4622-B821-5F40C774C924}"/>
+              <c16:uniqueId val="{00000001-EC29-4AD8-87BA-B245F37F6D94}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2141,11 +2314,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="18398648"/>
-        <c:axId val="99920468"/>
+        <c:axId val="88641036"/>
+        <c:axId val="16461264"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="18398648"/>
+        <c:axId val="88641036"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2194,7 +2367,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2220,7 +2393,7 @@
             <a:endParaRPr lang="es-419"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99920468"/>
+        <c:crossAx val="16461264"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2228,7 +2401,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="99920468"/>
+        <c:axId val="16461264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2277,7 +2450,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\)" sourceLinked="1"/>
+        <c:numFmt formatCode="\$#,##0.00" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2303,7 +2476,7 @@
             <a:endParaRPr lang="es-419"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="18398648"/>
+        <c:crossAx val="88641036"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2366,16 +2539,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>361950</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>211680</xdr:colOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>424920</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>134280</xdr:rowOff>
+      <xdr:rowOff>29310</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2407,16 +2580,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>322560</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>54360</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>30435</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>59400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2442,10 +2615,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2576,15 +2745,15 @@
     <v>1005.82</v>
     <v>0.90939999999999999</v>
     <v>-9.32</v>
-    <v>-1.7210000000000001E-3</v>
+    <v>-2.0010000000000002E-3</v>
     <v>-9.2390000000000007E-3</v>
-    <v>-1.72</v>
+    <v>-2</v>
     <v>443417364175</v>
     <v>1008.79</v>
     <v>Costco Wholesale Corporation (Costco) opera almacenes de membresía y sitios de comercio electrónico que ofrecen una selección de productos de marca nacional y de marca privada en una amplia gama de categorías. La Compañía compra la mayoría de sus mercancías directamente a los proveedores y la dirige a puntos de consolidación de cross-docking (depósitos) o directamente a sus almacenes. Opera 891 almacenes, incluyendo 614 en los Estados Unidos y Puerto Rico, 108 en Canadá, 40 en México, 35 en Japón, 29 en el Reino Unido, 19 en Corea, 15 en Australia, 14 en Taiwán, siete en China, y más. cinco en España, dos en Francia, y uno en Islandia, Nueva Zelanda y Suecia. También opera sitios de comercio electrónico en los Estados Unidos, Canadá, el Reino Unido, México, Corea, Taiwán, Japón y Australia. La Compañía ofrece una amplia selección de mercancías, además de la conveniencia de departamentos especializados y servicios exclusivos para miembros.</v>
     <v>341000</v>
     <v>XNAS</v>
-    <v>46153.850181238282</v>
+    <v>46153.999790890623</v>
     <v>Nasdaq Stock Market</v>
     <v>0</v>
     <v>1007</v>
@@ -2594,15 +2763,15 @@
     <v>USD</v>
     <v>COSTCO WHOLESALE CORPORATION</v>
     <v>COSTCO WHOLESALE CORPORATION</v>
-    <v>51.979399999999998</v>
+    <v>52.464199999999998</v>
     <v>999.47</v>
-    <v>997.75</v>
+    <v>997.47</v>
     <v>Diversified Retail</v>
     <v>999 Lake Dr, ISSAQUAH, WA, 98027- US</v>
     <v>COST</v>
     <v>Acciones</v>
     <v>COSTCO WHOLESALE CORPORATION (XNAS:COST)</v>
-    <v>2049558</v>
+    <v>2053529</v>
     <v>1785965</v>
   </rv>
   <rv s="2">
@@ -2806,9 +2975,9 @@
       <v xml:space="preserve">desde el cierre anterior </v>
       <v xml:space="preserve">al cierre </v>
       <v xml:space="preserve">desde el cierre anterior </v>
-      <v>Origen: Nasdaq Última venta</v>
+      <v>Origen: Nasdaq</v>
       <v xml:space="preserve">desde el cierre </v>
-      <v>Tiempo real Nasdaq Última venta</v>
+      <v>Retrasado 15 minutos</v>
       <v xml:space="preserve">desde el cierre </v>
       <v>GMT</v>
     </spb>
@@ -2967,18 +3136,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BDB7A695-0301-4C27-94B9-5CBC58DC4A48}" name="Tabla1" displayName="Tabla1" ref="I1:L2" totalsRowShown="0">
-  <autoFilter ref="I1:L2" xr:uid="{BDB7A695-0301-4C27-94B9-5CBC58DC4A48}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C49D2E2B-324B-46E7-B2A0-B757F8739393}" name="Tabla1" displayName="Tabla1" ref="J1:M2" totalsRowShown="0">
+  <autoFilter ref="J1:M2" xr:uid="{C49D2E2B-324B-46E7-B2A0-B757F8739393}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{F3EA13A3-C831-4DB4-BCE6-4A45E81C9711}" name="Ticker"/>
-    <tableColumn id="2" xr3:uid="{EDE7B658-91DF-43A0-B6AE-F44CC5962FCD}" name="Precio" dataDxfId="2">
-      <calculatedColumnFormula array="1">_FV(I2,"Precio")</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{8F34A657-98EE-421D-8464-6D1BEC47B25B}" name="Ticker"/>
+    <tableColumn id="2" xr3:uid="{E27D6F73-1936-49CF-8AD0-52CD4A172692}" name="Precio" dataDxfId="2">
+      <calculatedColumnFormula array="1">_FV(J2,"Precio")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{470A2378-CB3A-4DFD-A00B-508588A527C0}" name="P/E" dataDxfId="1">
-      <calculatedColumnFormula array="1">_FV(I2,"P/I",TRUE)</calculatedColumnFormula>
+    <tableColumn id="3" xr3:uid="{39BB10F9-A28F-4E20-AC64-E1D71534052E}" name="Ratio P/E" dataDxfId="1">
+      <calculatedColumnFormula array="1">_FV(J2,"P/I",TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{2CFFFEC1-1B22-4C45-86B7-4779917DC7BA}" name="Beta" dataDxfId="0">
-      <calculatedColumnFormula array="1">_FV(I2,"Beta")</calculatedColumnFormula>
+    <tableColumn id="4" xr3:uid="{3EC17C62-256C-415E-A5F4-C5099C1B411A}" name="Beta" dataDxfId="0">
+      <calculatedColumnFormula array="1">_FV(J2,"Beta")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -3168,16 +3337,17 @@
     <tabColor rgb="FFE040FB"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L54"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="30" customWidth="1"/>
-    <col min="9" max="9" width="47.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="47.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -3187,20 +3357,20 @@
       <c r="E1" s="14"/>
       <c r="F1" s="14"/>
       <c r="G1" s="14"/>
-      <c r="I1" t="s">
-        <v>139</v>
-      </c>
       <c r="J1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+      <c r="M1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>1</v>
       </c>
@@ -3210,23 +3380,23 @@
       <c r="E2" s="13"/>
       <c r="F2" s="13"/>
       <c r="G2" s="13"/>
-      <c r="I2" t="e" vm="1">
+      <c r="J2" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="J2" s="112" cm="1">
-        <f t="array" aca="1" ref="J2" ca="1">_FV(I2,"Precio")</f>
+      <c r="K2" s="154" cm="1">
+        <f t="array" aca="1" ref="K2" ca="1">_FV(J2,"Precio")</f>
         <v>999.47</v>
       </c>
-      <c r="K2" s="113" cm="1">
-        <f t="array" aca="1" ref="K2" ca="1">_FV(I2,"P/I",TRUE)</f>
-        <v>51.979399999999998</v>
-      </c>
-      <c r="L2" s="113" cm="1">
-        <f t="array" aca="1" ref="L2" ca="1">_FV(I2,"Beta")</f>
+      <c r="L2" s="155" cm="1">
+        <f t="array" aca="1" ref="L2" ca="1">_FV(J2,"P/I",TRUE)</f>
+        <v>52.464199999999998</v>
+      </c>
+      <c r="M2" s="155" cm="1">
+        <f t="array" aca="1" ref="M2" ca="1">_FV(J2,"Beta")</f>
         <v>0.90939999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>2</v>
       </c>
@@ -3241,20 +3411,20 @@
       <c r="F3" s="10"/>
       <c r="G3" s="10"/>
     </row>
-    <row r="4" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="16" cm="1">
-        <f t="array" aca="1" ref="B4" ca="1">_FV(I2,"Precio")</f>
+        <f t="array" aca="1" ref="B4" ca="1">Tabla1[Precio]</f>
         <v>999.47</v>
       </c>
       <c r="C4" s="15" t="s">
         <v>6</v>
       </c>
       <c r="D4" s="17" cm="1">
-        <f t="array" aca="1" ref="D4" ca="1">_FV(I2,"P/I",TRUE)</f>
-        <v>51.979399999999998</v>
+        <f t="array" aca="1" ref="D4" ca="1">Tabla1[Ratio P/E]</f>
+        <v>52.464199999999998</v>
       </c>
       <c r="E4" s="18" t="s">
         <v>7</v>
@@ -3264,7 +3434,7 @@
       </c>
       <c r="G4" s="9"/>
     </row>
-    <row r="5" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>9</v>
       </c>
@@ -3279,7 +3449,7 @@
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
     </row>
-    <row r="6" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>12</v>
       </c>
@@ -3290,7 +3460,7 @@
       <c r="F6" s="13"/>
       <c r="G6" s="13"/>
     </row>
-    <row r="7" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
         <v>13</v>
       </c>
@@ -3310,132 +3480,132 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="25" t="s">
         <v>19</v>
       </c>
       <c r="B8" s="26">
         <f ca="1">($B$4/$D$4)*15*(1-0*0.06)</f>
-        <v>288.4229136927321</v>
+        <v>285.75771669061953</v>
       </c>
       <c r="C8" s="26">
         <f ca="1">($B$4/$D$4)*25*(1-0*0.06)</f>
-        <v>480.70485615455357</v>
+        <v>476.26286115103255</v>
       </c>
       <c r="D8" s="26">
         <f ca="1">($B$4/$D$4)*35*(1-0*0.06)</f>
-        <v>672.98679861637493</v>
+        <v>666.76800561144557</v>
       </c>
       <c r="E8" s="26">
         <f ca="1">($B$4/$D$4)*50*(1-0*0.06)</f>
-        <v>961.40971230910714</v>
+        <v>952.52572230206511</v>
       </c>
       <c r="F8" s="26">
         <f ca="1">($B$4/$D$4)*60*(1-0*0.06)</f>
-        <v>1153.6916547709284</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1143.0308667624781</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="27" t="s">
         <v>20</v>
       </c>
       <c r="B9" s="28">
         <f ca="1">($B$4/$D$4)*15*(1-0.005*0.06)</f>
-        <v>288.33638681862431</v>
+        <v>285.67198937561233</v>
       </c>
       <c r="C9" s="28">
         <f ca="1">($B$4/$D$4)*25*(1-0.005*0.06)</f>
-        <v>480.56064469770723</v>
+        <v>476.11998229268727</v>
       </c>
       <c r="D9" s="28">
         <f ca="1">($B$4/$D$4)*35*(1-0.005*0.06)</f>
-        <v>672.78490257679005</v>
+        <v>666.56797520976215</v>
       </c>
       <c r="E9" s="28">
         <f ca="1">($B$4/$D$4)*50*(1-0.005*0.06)</f>
-        <v>961.12128939541446</v>
+        <v>952.23996458537454</v>
       </c>
       <c r="F9" s="28">
         <f ca="1">($B$4/$D$4)*60*(1-0.005*0.06)</f>
-        <v>1153.3455472744972</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1142.6879575024493</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="29" t="s">
         <v>21</v>
       </c>
       <c r="B10" s="30">
         <f ca="1">($B$4/$D$4)*15*(1-0.01*0.06)</f>
-        <v>288.24985994451646</v>
+        <v>285.58626206060512</v>
       </c>
       <c r="C10" s="30">
         <f ca="1">($B$4/$D$4)*25*(1-0.01*0.06)</f>
-        <v>480.41643324086084</v>
+        <v>475.97710343434193</v>
       </c>
       <c r="D10" s="30">
         <f ca="1">($B$4/$D$4)*35*(1-0.01*0.06)</f>
-        <v>672.58300653720505</v>
+        <v>666.36794480807873</v>
       </c>
       <c r="E10" s="30">
         <f ca="1">($B$4/$D$4)*50*(1-0.01*0.06)</f>
-        <v>960.83286648172168</v>
+        <v>951.95420686868385</v>
       </c>
       <c r="F10" s="30">
         <f ca="1">($B$4/$D$4)*60*(1-0.01*0.06)</f>
-        <v>1152.9994397780658</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1142.3450482424205</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B11" s="32">
         <f ca="1">($B$4/$D$4)*15*(1-0.025*0.06)</f>
-        <v>287.99027932219303</v>
+        <v>285.32908011558362</v>
       </c>
       <c r="C11" s="32">
         <f ca="1">($B$4/$D$4)*25*(1-0.025*0.06)</f>
-        <v>479.98379887032178</v>
+        <v>475.54846685930602</v>
       </c>
       <c r="D11" s="32">
         <f ca="1">($B$4/$D$4)*35*(1-0.025*0.06)</f>
-        <v>671.97731841845041</v>
+        <v>665.76785360302847</v>
       </c>
       <c r="E11" s="32">
         <f ca="1">($B$4/$D$4)*50*(1-0.025*0.06)</f>
-        <v>959.96759774064355</v>
+        <v>951.09693371861204</v>
       </c>
       <c r="F11" s="32">
         <f ca="1">($B$4/$D$4)*60*(1-0.025*0.06)</f>
-        <v>1151.9611172887721</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1141.3163204623345</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="33" t="s">
         <v>23</v>
       </c>
       <c r="B12" s="34">
         <f ca="1">($B$4/$D$4)*15*(1-0.05*0.06)</f>
-        <v>287.55764495165391</v>
+        <v>284.90044354054766</v>
       </c>
       <c r="C12" s="34">
         <f ca="1">($B$4/$D$4)*25*(1-0.05*0.06)</f>
-        <v>479.26274158608993</v>
+        <v>474.83407256757943</v>
       </c>
       <c r="D12" s="34">
         <f ca="1">($B$4/$D$4)*35*(1-0.05*0.06)</f>
-        <v>670.96783822052578</v>
+        <v>664.76770159461125</v>
       </c>
       <c r="E12" s="34">
         <f ca="1">($B$4/$D$4)*50*(1-0.05*0.06)</f>
-        <v>958.52548317217986</v>
+        <v>949.66814513515885</v>
       </c>
       <c r="F12" s="34">
         <f ca="1">($B$4/$D$4)*60*(1-0.05*0.06)</f>
-        <v>1150.2305798066157</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1139.6017741621906</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>24</v>
       </c>
@@ -3446,7 +3616,7 @@
       <c r="F13" s="13"/>
       <c r="G13" s="13"/>
     </row>
-    <row r="14" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
         <v>13</v>
       </c>
@@ -3466,54 +3636,54 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="25" t="s">
         <v>19</v>
       </c>
       <c r="B15" s="35">
         <f t="shared" ref="B15:F19" ca="1" si="0">(B8-$B$4)/$B$4</f>
-        <v>-0.71142414110205199</v>
+        <v>-0.71409075140762657</v>
       </c>
       <c r="C15" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.51904023517008657</v>
+        <v>-0.5234845856793775</v>
       </c>
       <c r="D15" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.32665632923812132</v>
+        <v>-0.33287841995112855</v>
       </c>
       <c r="E15" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>-3.8080470340173179E-2</v>
+        <v>-4.6969171358755057E-2</v>
       </c>
       <c r="F15" s="35">
         <f t="shared" ca="1" si="0"/>
-        <v>0.15430343559179199</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.14363699436949393</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="27" t="s">
         <v>20</v>
       </c>
       <c r="B16" s="36">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.71151071385972131</v>
+        <v>-0.71417652418220423</v>
       </c>
       <c r="C16" s="36">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.51918452309953556</v>
+        <v>-0.52362754030367364</v>
       </c>
       <c r="D16" s="36">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.32685833233934986</v>
+        <v>-0.33307855642514317</v>
       </c>
       <c r="E16" s="36">
         <f t="shared" ca="1" si="0"/>
-        <v>-3.8369046199071069E-2</v>
+        <v>-4.7255080607347386E-2</v>
       </c>
       <c r="F16" s="36">
         <f t="shared" ca="1" si="0"/>
-        <v>0.15395714456111459</v>
+        <v>0.14329390327118299</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3522,23 +3692,23 @@
       </c>
       <c r="B17" s="37">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.71159728661739086</v>
+        <v>-0.71426229695678201</v>
       </c>
       <c r="C17" s="37">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.51932881102898443</v>
+        <v>-0.52377049492797001</v>
       </c>
       <c r="D17" s="37">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.3270603354405785</v>
+        <v>-0.33327869289915785</v>
       </c>
       <c r="E17" s="37">
         <f t="shared" ca="1" si="0"/>
-        <v>-3.865762205796907E-2</v>
+        <v>-4.7540989855939818E-2</v>
       </c>
       <c r="F17" s="37">
         <f t="shared" ca="1" si="0"/>
-        <v>0.15361085353043694</v>
+        <v>0.14295081217287209</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3547,23 +3717,23 @@
       </c>
       <c r="B18" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.71185700489039894</v>
+        <v>-0.71451961528051511</v>
       </c>
       <c r="C18" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.51976167481733138</v>
+        <v>-0.52419935880085844</v>
       </c>
       <c r="D18" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.32766634474426409</v>
+        <v>-0.33387910232120177</v>
       </c>
       <c r="E18" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>-3.9523349634662842E-2</v>
+        <v>-4.8398717601716899E-2</v>
       </c>
       <c r="F18" s="38">
         <f t="shared" ca="1" si="0"/>
-        <v>0.15257198043840445</v>
+        <v>0.14192153887793976</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -3572,23 +3742,23 @@
       </c>
       <c r="B19" s="39">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.71228986867874589</v>
+        <v>-0.71494847915340365</v>
       </c>
       <c r="C19" s="39">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.52048311446457629</v>
+        <v>-0.52491413192233949</v>
       </c>
       <c r="D19" s="39">
         <f t="shared" ca="1" si="0"/>
-        <v>-0.32867636025040697</v>
+        <v>-0.33487978469127516</v>
       </c>
       <c r="E19" s="39">
         <f t="shared" ca="1" si="0"/>
-        <v>-4.0966228929152616E-2</v>
+        <v>-4.9828263844678852E-2</v>
       </c>
       <c r="F19" s="39">
         <f t="shared" ca="1" si="0"/>
-        <v>0.15084052528501668</v>
+        <v>0.14020608338638538</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3718,64 +3888,64 @@
       <c r="A29" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="B29" s="95" t="s">
+      <c r="B29" s="133" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="95"/>
-      <c r="D29" s="95"/>
-      <c r="E29" s="95"/>
-      <c r="F29" s="95"/>
-      <c r="G29" s="95"/>
+      <c r="C29" s="133"/>
+      <c r="D29" s="133"/>
+      <c r="E29" s="133"/>
+      <c r="F29" s="133"/>
+      <c r="G29" s="133"/>
     </row>
     <row r="30" spans="1:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="52" t="s">
         <v>48</v>
       </c>
-      <c r="B30" s="96" t="s">
+      <c r="B30" s="134" t="s">
         <v>49</v>
       </c>
-      <c r="C30" s="96"/>
-      <c r="D30" s="96"/>
-      <c r="E30" s="96"/>
-      <c r="F30" s="96"/>
-      <c r="G30" s="96"/>
+      <c r="C30" s="134"/>
+      <c r="D30" s="134"/>
+      <c r="E30" s="134"/>
+      <c r="F30" s="134"/>
+      <c r="G30" s="134"/>
     </row>
     <row r="31" spans="1:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="B31" s="95" t="s">
+      <c r="B31" s="133" t="s">
         <v>51</v>
       </c>
-      <c r="C31" s="95"/>
-      <c r="D31" s="95"/>
-      <c r="E31" s="95"/>
-      <c r="F31" s="95"/>
-      <c r="G31" s="95"/>
+      <c r="C31" s="133"/>
+      <c r="D31" s="133"/>
+      <c r="E31" s="133"/>
+      <c r="F31" s="133"/>
+      <c r="G31" s="133"/>
     </row>
     <row r="32" spans="1:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="B32" s="96" t="s">
+      <c r="B32" s="134" t="s">
         <v>53</v>
       </c>
-      <c r="C32" s="96"/>
-      <c r="D32" s="96"/>
-      <c r="E32" s="96"/>
-      <c r="F32" s="96"/>
-      <c r="G32" s="96"/>
+      <c r="C32" s="134"/>
+      <c r="D32" s="134"/>
+      <c r="E32" s="134"/>
+      <c r="F32" s="134"/>
+      <c r="G32" s="134"/>
     </row>
     <row r="33" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="97" t="s">
+      <c r="A33" s="135" t="s">
         <v>54</v>
       </c>
-      <c r="B33" s="97"/>
-      <c r="C33" s="97"/>
-      <c r="D33" s="97"/>
-      <c r="E33" s="97"/>
-      <c r="F33" s="97"/>
-      <c r="G33" s="97"/>
+      <c r="B33" s="135"/>
+      <c r="C33" s="135"/>
+      <c r="D33" s="135"/>
+      <c r="E33" s="135"/>
+      <c r="F33" s="135"/>
+      <c r="G33" s="135"/>
     </row>
     <row r="34" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3851,636 +4021,850 @@
   <sheetPr>
     <tabColor rgb="FF64B5F6"/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="8" width="14" customWidth="1"/>
-    <col min="9" max="10" width="18" customWidth="1"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="5" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="98" t="s">
+    <row r="1" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="136" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="98"/>
-      <c r="C1" s="98"/>
-      <c r="D1" s="98"/>
-      <c r="E1" s="98"/>
-      <c r="F1" s="98"/>
-      <c r="G1" s="98"/>
-      <c r="H1" s="98"/>
-      <c r="I1" s="98"/>
-      <c r="J1" s="98"/>
-    </row>
-    <row r="2" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="99" t="s">
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
+      <c r="I1" s="136"/>
+      <c r="J1" s="136"/>
+      <c r="K1" s="53">
+        <f ca="1">'Matriz de Sensibilidad'!$B$4/'Matriz de Sensibilidad'!$D$4</f>
+        <v>19.050514446041301</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="137" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="99"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-    </row>
-    <row r="3" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="53" t="s">
+      <c r="B2" s="137"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
+      <c r="E2" s="137"/>
+      <c r="F2" s="137"/>
+      <c r="G2" s="137"/>
+      <c r="H2" s="137"/>
+      <c r="I2" s="137"/>
+      <c r="J2" s="137"/>
+      <c r="K2" s="53">
+        <f ca="1">'Matriz de Sensibilidad'!$B$4</f>
+        <v>999.47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="54" t="s">
         <v>57</v>
       </c>
-      <c r="B3" s="54">
-        <f ca="1">'Matriz de Sensibilidad'!B4</f>
+      <c r="B3" s="55">
+        <f ca="1">'Matriz de Sensibilidad'!$B$4</f>
         <v>999.47</v>
       </c>
-      <c r="C3" s="55" t="s">
+      <c r="C3" s="138" t="s">
         <v>58</v>
       </c>
-      <c r="D3" s="100" t="s">
+      <c r="D3" s="138"/>
+      <c r="E3" s="138"/>
+      <c r="F3" s="138"/>
+      <c r="G3" s="138"/>
+      <c r="H3" s="138"/>
+      <c r="I3" s="138"/>
+      <c r="J3" s="138"/>
+      <c r="K3" s="56">
+        <f ca="1">'Matriz de Sensibilidad'!$D$4</f>
+        <v>52.464199999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="E3" s="100"/>
-      <c r="F3" s="100"/>
-      <c r="G3" s="100"/>
-      <c r="H3" s="100"/>
-      <c r="I3" s="100"/>
-      <c r="J3" s="100"/>
-    </row>
-    <row r="4" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="53" t="s">
+      <c r="B4" s="57">
+        <f ca="1">'Matriz de Sensibilidad'!$D$4</f>
+        <v>52.464199999999998</v>
+      </c>
+      <c r="C4" s="138" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="56">
-        <f ca="1">'Matriz de Sensibilidad'!D4</f>
-        <v>51.979399999999998</v>
-      </c>
-      <c r="C4" s="55" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" s="100" t="s">
+      <c r="D4" s="138"/>
+      <c r="E4" s="138"/>
+      <c r="F4" s="138"/>
+      <c r="G4" s="138"/>
+      <c r="H4" s="138"/>
+      <c r="I4" s="138"/>
+      <c r="J4" s="138"/>
+    </row>
+    <row r="5" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="54" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="55">
+        <f ca="1">'Matriz de Sensibilidad'!$B$4/'Matriz de Sensibilidad'!$D$4</f>
+        <v>19.050514446041301</v>
+      </c>
+      <c r="C5" s="138" t="s">
         <v>61</v>
       </c>
-      <c r="E4" s="100"/>
-      <c r="F4" s="100"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="100"/>
-      <c r="J4" s="100"/>
-    </row>
-    <row r="5" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="53" t="s">
+      <c r="D5" s="138"/>
+      <c r="E5" s="138"/>
+      <c r="F5" s="138"/>
+      <c r="G5" s="138"/>
+      <c r="H5" s="138"/>
+      <c r="I5" s="138"/>
+      <c r="J5" s="138"/>
+    </row>
+    <row r="6" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="54" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="56">
+      <c r="B6" s="58">
         <v>38</v>
       </c>
-      <c r="C5" s="55" t="s">
-        <v>58</v>
-      </c>
-      <c r="D5" s="100" t="s">
+      <c r="C6" s="138" t="s">
         <v>63</v>
       </c>
-      <c r="E5" s="100"/>
-      <c r="F5" s="100"/>
-      <c r="G5" s="100"/>
-      <c r="H5" s="100"/>
-      <c r="I5" s="100"/>
-      <c r="J5" s="100"/>
-    </row>
-    <row r="6" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="53" t="s">
+      <c r="D6" s="138"/>
+      <c r="E6" s="138"/>
+      <c r="F6" s="138"/>
+      <c r="G6" s="138"/>
+      <c r="H6" s="138"/>
+      <c r="I6" s="138"/>
+      <c r="J6" s="138"/>
+    </row>
+    <row r="7" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="54" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="57">
+      <c r="B7" s="59">
         <v>9</v>
       </c>
-      <c r="C6" s="55" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="100" t="s">
+      <c r="C7" s="138" t="s">
         <v>65</v>
       </c>
-      <c r="E6" s="100"/>
-      <c r="F6" s="100"/>
-      <c r="G6" s="100"/>
-      <c r="H6" s="100"/>
-      <c r="I6" s="100"/>
-      <c r="J6" s="100"/>
-    </row>
-    <row r="7" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="53" t="s">
+      <c r="D7" s="138"/>
+      <c r="E7" s="138"/>
+      <c r="F7" s="138"/>
+      <c r="G7" s="138"/>
+      <c r="H7" s="138"/>
+      <c r="I7" s="138"/>
+      <c r="J7" s="138"/>
+    </row>
+    <row r="8" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="54" t="s">
         <v>66</v>
       </c>
-      <c r="B7" s="58">
+      <c r="B8" s="60">
         <v>0.01</v>
       </c>
-      <c r="C7" s="55" t="s">
-        <v>58</v>
-      </c>
-      <c r="D7" s="100" t="s">
+      <c r="C8" s="138" t="s">
         <v>67</v>
       </c>
-      <c r="E7" s="100"/>
-      <c r="F7" s="100"/>
-      <c r="G7" s="100"/>
-      <c r="H7" s="100"/>
-      <c r="I7" s="100"/>
-      <c r="J7" s="100"/>
-    </row>
-    <row r="8" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="53" t="s">
+      <c r="D8" s="138"/>
+      <c r="E8" s="138"/>
+      <c r="F8" s="138"/>
+      <c r="G8" s="138"/>
+      <c r="H8" s="138"/>
+      <c r="I8" s="138"/>
+      <c r="J8" s="138"/>
+    </row>
+    <row r="9" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="54" t="s">
         <v>68</v>
       </c>
-      <c r="B8" s="58">
+      <c r="B9" s="60">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="C8" s="55" t="s">
-        <v>58</v>
-      </c>
-      <c r="D8" s="100" t="s">
+      <c r="C9" s="138" t="s">
         <v>69</v>
       </c>
-      <c r="E8" s="100"/>
-      <c r="F8" s="100"/>
-      <c r="G8" s="100"/>
-      <c r="H8" s="100"/>
-      <c r="I8" s="100"/>
-      <c r="J8" s="100"/>
-    </row>
-    <row r="10" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="99" t="s">
+      <c r="D9" s="138"/>
+      <c r="E9" s="138"/>
+      <c r="F9" s="138"/>
+      <c r="G9" s="138"/>
+      <c r="H9" s="138"/>
+      <c r="I9" s="138"/>
+      <c r="J9" s="138"/>
+    </row>
+    <row r="11" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="137" t="s">
         <v>70</v>
       </c>
-      <c r="B10" s="99"/>
-      <c r="C10" s="99"/>
-      <c r="D10" s="99"/>
-      <c r="E10" s="99"/>
-      <c r="F10" s="99"/>
-      <c r="G10" s="99"/>
-      <c r="H10" s="99"/>
-      <c r="I10" s="99"/>
-      <c r="J10" s="99"/>
-    </row>
-    <row r="11" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="59" t="s">
+      <c r="B11" s="137"/>
+      <c r="C11" s="137"/>
+      <c r="D11" s="137"/>
+      <c r="E11" s="137"/>
+      <c r="F11" s="137"/>
+      <c r="G11" s="137"/>
+      <c r="H11" s="137"/>
+      <c r="I11" s="137"/>
+      <c r="J11" s="137"/>
+    </row>
+    <row r="12" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="61" t="s">
         <v>71</v>
       </c>
-      <c r="B11" s="59" t="s">
+      <c r="B12" s="61" t="s">
         <v>72</v>
       </c>
-      <c r="C11" s="101" t="s">
+      <c r="C12" s="139" t="s">
         <v>73</v>
       </c>
-      <c r="D11" s="101"/>
-      <c r="E11" s="101"/>
-      <c r="F11" s="101"/>
-      <c r="G11" s="101"/>
-      <c r="H11" s="101"/>
-      <c r="I11" s="101"/>
-      <c r="J11" s="101"/>
-    </row>
-    <row r="12" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="60" t="s">
+      <c r="D12" s="139"/>
+      <c r="E12" s="139"/>
+      <c r="F12" s="139"/>
+      <c r="G12" s="139"/>
+      <c r="H12" s="139"/>
+      <c r="I12" s="139"/>
+      <c r="J12" s="139"/>
+    </row>
+    <row r="13" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="62" t="s">
         <v>74</v>
       </c>
-      <c r="B12" s="61">
-        <v>598.78095134615501</v>
-      </c>
-      <c r="C12" s="102" t="s">
+      <c r="B13" s="63">
+        <v>731.28195040169999</v>
+      </c>
+      <c r="C13" s="140" t="s">
         <v>75</v>
       </c>
-      <c r="D12" s="102"/>
-      <c r="E12" s="102"/>
-      <c r="F12" s="102"/>
-      <c r="G12" s="102"/>
-      <c r="H12" s="102"/>
-      <c r="I12" s="102"/>
-      <c r="J12" s="102"/>
-    </row>
-    <row r="13" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="62" t="s">
+      <c r="D13" s="140"/>
+      <c r="E13" s="140"/>
+      <c r="F13" s="140"/>
+      <c r="G13" s="140"/>
+      <c r="H13" s="140"/>
+      <c r="I13" s="140"/>
+      <c r="J13" s="140"/>
+    </row>
+    <row r="14" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="64" t="s">
         <v>76</v>
       </c>
-      <c r="B13" s="63">
-        <v>598.70959401651498</v>
-      </c>
-      <c r="C13" s="103" t="s">
+      <c r="B14" s="65">
+        <v>731.19480279442098</v>
+      </c>
+      <c r="C14" s="141" t="s">
         <v>77</v>
       </c>
-      <c r="D13" s="103"/>
-      <c r="E13" s="103"/>
-      <c r="F13" s="103"/>
-      <c r="G13" s="103"/>
-      <c r="H13" s="103"/>
-      <c r="I13" s="103"/>
-      <c r="J13" s="103"/>
-    </row>
-    <row r="14" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="64" t="s">
+      <c r="D14" s="141"/>
+      <c r="E14" s="141"/>
+      <c r="F14" s="141"/>
+      <c r="G14" s="141"/>
+      <c r="H14" s="141"/>
+      <c r="I14" s="141"/>
+      <c r="J14" s="141"/>
+    </row>
+    <row r="15" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="66" t="s">
         <v>78</v>
       </c>
-      <c r="B14" s="65">
-        <v>138.64326208939701</v>
-      </c>
-      <c r="C14" s="104" t="s">
+      <c r="B15" s="67">
+        <v>169.32287989932499</v>
+      </c>
+      <c r="C15" s="142" t="s">
         <v>79</v>
       </c>
-      <c r="D14" s="104"/>
-      <c r="E14" s="104"/>
-      <c r="F14" s="104"/>
-      <c r="G14" s="104"/>
-      <c r="H14" s="104"/>
-      <c r="I14" s="104"/>
-      <c r="J14" s="104"/>
-    </row>
-    <row r="15" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="66" t="s">
+      <c r="D15" s="142"/>
+      <c r="E15" s="142"/>
+      <c r="F15" s="142"/>
+      <c r="G15" s="142"/>
+      <c r="H15" s="142"/>
+      <c r="I15" s="142"/>
+      <c r="J15" s="142"/>
+    </row>
+    <row r="16" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="68" t="s">
         <v>80</v>
       </c>
-      <c r="B15" s="67">
-        <v>373.023888775437</v>
-      </c>
-      <c r="C15" s="105" t="s">
+      <c r="B16" s="69">
+        <v>455.56832814548102</v>
+      </c>
+      <c r="C16" s="143" t="s">
         <v>81</v>
       </c>
-      <c r="D15" s="105"/>
-      <c r="E15" s="105"/>
-      <c r="F15" s="105"/>
-      <c r="G15" s="105"/>
-      <c r="H15" s="105"/>
-      <c r="I15" s="105"/>
-      <c r="J15" s="105"/>
-    </row>
-    <row r="16" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="68" t="s">
+      <c r="D16" s="143"/>
+      <c r="E16" s="143"/>
+      <c r="F16" s="143"/>
+      <c r="G16" s="143"/>
+      <c r="H16" s="143"/>
+      <c r="I16" s="143"/>
+      <c r="J16" s="143"/>
+    </row>
+    <row r="17" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="70" t="s">
         <v>82</v>
       </c>
-      <c r="B16" s="69">
-        <v>505.28285927806701</v>
-      </c>
-      <c r="C16" s="106" t="s">
+      <c r="B17" s="71">
+        <v>617.094171093299</v>
+      </c>
+      <c r="C17" s="144" t="s">
         <v>83</v>
       </c>
-      <c r="D16" s="106"/>
-      <c r="E16" s="106"/>
-      <c r="F16" s="106"/>
-      <c r="G16" s="106"/>
-      <c r="H16" s="106"/>
-      <c r="I16" s="106"/>
-      <c r="J16" s="106"/>
-    </row>
-    <row r="17" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="62" t="s">
+      <c r="D17" s="144"/>
+      <c r="E17" s="144"/>
+      <c r="F17" s="144"/>
+      <c r="G17" s="144"/>
+      <c r="H17" s="144"/>
+      <c r="I17" s="144"/>
+      <c r="J17" s="144"/>
+    </row>
+    <row r="18" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="64" t="s">
         <v>84</v>
       </c>
-      <c r="B17" s="63">
-        <v>688.85409076321105</v>
-      </c>
-      <c r="C17" s="103" t="s">
+      <c r="B18" s="65">
+        <v>841.28688780597997</v>
+      </c>
+      <c r="C18" s="141" t="s">
         <v>85</v>
       </c>
-      <c r="D17" s="103"/>
-      <c r="E17" s="103"/>
-      <c r="F17" s="103"/>
-      <c r="G17" s="103"/>
-      <c r="H17" s="103"/>
-      <c r="I17" s="103"/>
-      <c r="J17" s="103"/>
-    </row>
-    <row r="18" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="66" t="s">
+      <c r="D18" s="141"/>
+      <c r="E18" s="141"/>
+      <c r="F18" s="141"/>
+      <c r="G18" s="141"/>
+      <c r="H18" s="141"/>
+      <c r="I18" s="141"/>
+      <c r="J18" s="141"/>
+    </row>
+    <row r="19" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="68" t="s">
         <v>86</v>
       </c>
-      <c r="B18" s="67">
-        <v>829.16575850583104</v>
-      </c>
-      <c r="C18" s="105" t="s">
+      <c r="B19" s="69">
+        <v>1012.6473658243</v>
+      </c>
+      <c r="C19" s="143" t="s">
         <v>87</v>
       </c>
-      <c r="D18" s="105"/>
-      <c r="E18" s="105"/>
-      <c r="F18" s="105"/>
-      <c r="G18" s="105"/>
-      <c r="H18" s="105"/>
-      <c r="I18" s="105"/>
-      <c r="J18" s="105"/>
-    </row>
-    <row r="19" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="70" t="s">
-        <v>88</v>
-      </c>
-      <c r="B19" s="71">
-        <v>0.90149999999999997</v>
-      </c>
-      <c r="C19" s="107" t="s">
-        <v>89</v>
-      </c>
-      <c r="D19" s="107"/>
-      <c r="E19" s="107"/>
-      <c r="F19" s="107"/>
-      <c r="G19" s="107"/>
-      <c r="H19" s="107"/>
-      <c r="I19" s="107"/>
-      <c r="J19" s="107"/>
+      <c r="D19" s="143"/>
+      <c r="E19" s="143"/>
+      <c r="F19" s="143"/>
+      <c r="G19" s="143"/>
+      <c r="H19" s="143"/>
+      <c r="I19" s="143"/>
+      <c r="J19" s="143"/>
     </row>
     <row r="20" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="72" t="s">
+        <v>88</v>
+      </c>
+      <c r="B20" s="73">
+        <v>0.93799999999999994</v>
+      </c>
+      <c r="C20" s="145" t="s">
+        <v>89</v>
+      </c>
+      <c r="D20" s="145"/>
+      <c r="E20" s="145"/>
+      <c r="F20" s="145"/>
+      <c r="G20" s="145"/>
+      <c r="H20" s="145"/>
+      <c r="I20" s="145"/>
+      <c r="J20" s="145"/>
+    </row>
+    <row r="21" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="74" t="s">
         <v>90</v>
       </c>
-      <c r="B20" s="73">
-        <v>3.0499999999999999E-2</v>
-      </c>
-      <c r="C20" s="108" t="s">
+      <c r="B21" s="75">
+        <v>1.4E-2</v>
+      </c>
+      <c r="C21" s="146" t="s">
         <v>91</v>
       </c>
-      <c r="D20" s="108"/>
-      <c r="E20" s="108"/>
-      <c r="F20" s="108"/>
-      <c r="G20" s="108"/>
-      <c r="H20" s="108"/>
-      <c r="I20" s="108"/>
-      <c r="J20" s="108"/>
-    </row>
-    <row r="22" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="99" t="s">
+      <c r="D21" s="146"/>
+      <c r="E21" s="146"/>
+      <c r="F21" s="146"/>
+      <c r="G21" s="146"/>
+      <c r="H21" s="146"/>
+      <c r="I21" s="146"/>
+      <c r="J21" s="146"/>
+    </row>
+    <row r="22" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="147" t="s">
         <v>92</v>
       </c>
-      <c r="B22" s="99"/>
-      <c r="C22" s="99"/>
-      <c r="D22" s="99"/>
-      <c r="E22" s="99"/>
-      <c r="F22" s="99"/>
-      <c r="G22" s="99"/>
-      <c r="H22" s="99"/>
-      <c r="I22" s="99"/>
-      <c r="J22" s="99"/>
-    </row>
-    <row r="23" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="59" t="s">
+      <c r="B22" s="147"/>
+      <c r="C22" s="147"/>
+      <c r="D22" s="147"/>
+      <c r="E22" s="147"/>
+      <c r="F22" s="147"/>
+      <c r="G22" s="147"/>
+      <c r="H22" s="147"/>
+      <c r="I22" s="147"/>
+      <c r="J22" s="147"/>
+    </row>
+    <row r="23" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="137" t="s">
         <v>93</v>
       </c>
-      <c r="B23" s="59" t="s">
+      <c r="B23" s="137"/>
+      <c r="C23" s="137"/>
+      <c r="D23" s="137"/>
+      <c r="E23" s="137"/>
+      <c r="F23" s="137"/>
+      <c r="G23" s="137"/>
+      <c r="H23" s="137"/>
+      <c r="I23" s="137"/>
+      <c r="J23" s="137"/>
+    </row>
+    <row r="24" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="61" t="s">
         <v>94</v>
       </c>
-      <c r="C23" s="59" t="s">
+      <c r="B24" s="61" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="74" t="s">
+      <c r="C24" s="139" t="s">
         <v>96</v>
       </c>
-      <c r="B24" s="75">
+      <c r="D24" s="139"/>
+      <c r="E24" s="139"/>
+      <c r="F24" s="139"/>
+      <c r="G24" s="139"/>
+      <c r="H24" s="139"/>
+      <c r="I24" s="139"/>
+      <c r="J24" s="139"/>
+    </row>
+    <row r="25" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="76" t="s">
+        <v>97</v>
+      </c>
+      <c r="B25" s="77">
         <v>6</v>
       </c>
-      <c r="C24" s="76">
+      <c r="C25" s="148">
         <v>3.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="74" t="s">
-        <v>97</v>
-      </c>
-      <c r="B25" s="75">
-        <v>7</v>
-      </c>
-      <c r="C25" s="76">
-        <v>3.5000000000000001E-3</v>
-      </c>
+      <c r="D25" s="148"/>
+      <c r="E25" s="148"/>
+      <c r="F25" s="148"/>
+      <c r="G25" s="148"/>
+      <c r="H25" s="148"/>
+      <c r="I25" s="148"/>
+      <c r="J25" s="148"/>
     </row>
     <row r="26" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="74" t="s">
+      <c r="A26" s="76" t="s">
         <v>98</v>
       </c>
-      <c r="B26" s="75">
-        <v>9</v>
-      </c>
-      <c r="C26" s="76">
-        <v>4.4999999999999997E-3</v>
-      </c>
+      <c r="B26" s="77">
+        <v>8</v>
+      </c>
+      <c r="C26" s="148">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="D26" s="148"/>
+      <c r="E26" s="148"/>
+      <c r="F26" s="148"/>
+      <c r="G26" s="148"/>
+      <c r="H26" s="148"/>
+      <c r="I26" s="148"/>
+      <c r="J26" s="148"/>
     </row>
     <row r="27" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="74" t="s">
+      <c r="A27" s="76" t="s">
         <v>99</v>
       </c>
-      <c r="B27" s="75">
-        <v>31</v>
-      </c>
-      <c r="C27" s="76">
-        <v>1.55E-2</v>
-      </c>
+      <c r="B27" s="77">
+        <v>8</v>
+      </c>
+      <c r="C27" s="148">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="D27" s="148"/>
+      <c r="E27" s="148"/>
+      <c r="F27" s="148"/>
+      <c r="G27" s="148"/>
+      <c r="H27" s="148"/>
+      <c r="I27" s="148"/>
+      <c r="J27" s="148"/>
     </row>
     <row r="28" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="74" t="s">
+      <c r="A28" s="76" t="s">
         <v>100</v>
       </c>
-      <c r="B28" s="75">
-        <v>65</v>
-      </c>
-      <c r="C28" s="76">
-        <v>3.2500000000000001E-2</v>
-      </c>
+      <c r="B28" s="77">
+        <v>32</v>
+      </c>
+      <c r="C28" s="148">
+        <v>1.6E-2</v>
+      </c>
+      <c r="D28" s="148"/>
+      <c r="E28" s="148"/>
+      <c r="F28" s="148"/>
+      <c r="G28" s="148"/>
+      <c r="H28" s="148"/>
+      <c r="I28" s="148"/>
+      <c r="J28" s="148"/>
     </row>
     <row r="29" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="74" t="s">
+      <c r="A29" s="76" t="s">
         <v>101</v>
       </c>
-      <c r="B29" s="75">
+      <c r="B29" s="77">
+        <v>66</v>
+      </c>
+      <c r="C29" s="148">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="D29" s="148"/>
+      <c r="E29" s="148"/>
+      <c r="F29" s="148"/>
+      <c r="G29" s="148"/>
+      <c r="H29" s="148"/>
+      <c r="I29" s="148"/>
+      <c r="J29" s="148"/>
+    </row>
+    <row r="30" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="76" t="s">
+        <v>102</v>
+      </c>
+      <c r="B30" s="77">
+        <v>102</v>
+      </c>
+      <c r="C30" s="148">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="D30" s="148"/>
+      <c r="E30" s="148"/>
+      <c r="F30" s="148"/>
+      <c r="G30" s="148"/>
+      <c r="H30" s="148"/>
+      <c r="I30" s="148"/>
+      <c r="J30" s="148"/>
+    </row>
+    <row r="31" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="76" t="s">
         <v>103</v>
       </c>
-      <c r="C29" s="76">
-        <v>5.1499999999999997E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="74" t="s">
-        <v>102</v>
-      </c>
-      <c r="B30" s="75">
-        <v>157</v>
-      </c>
-      <c r="C30" s="76">
-        <v>7.85E-2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="74" t="s">
-        <v>103</v>
-      </c>
-      <c r="B31" s="75">
-        <v>229</v>
-      </c>
-      <c r="C31" s="76">
-        <v>0.1145</v>
-      </c>
+      <c r="B31" s="77">
+        <v>156</v>
+      </c>
+      <c r="C31" s="148">
+        <v>7.8E-2</v>
+      </c>
+      <c r="D31" s="148"/>
+      <c r="E31" s="148"/>
+      <c r="F31" s="148"/>
+      <c r="G31" s="148"/>
+      <c r="H31" s="148"/>
+      <c r="I31" s="148"/>
+      <c r="J31" s="148"/>
     </row>
     <row r="32" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="74" t="s">
+      <c r="A32" s="76" t="s">
         <v>104</v>
       </c>
-      <c r="B32" s="75">
-        <v>245</v>
-      </c>
-      <c r="C32" s="76">
-        <v>0.1225</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="74" t="s">
+      <c r="B32" s="77">
+        <v>233</v>
+      </c>
+      <c r="C32" s="148">
+        <v>0.11650000000000001</v>
+      </c>
+      <c r="D32" s="148"/>
+      <c r="E32" s="148"/>
+      <c r="F32" s="148"/>
+      <c r="G32" s="148"/>
+      <c r="H32" s="148"/>
+      <c r="I32" s="148"/>
+      <c r="J32" s="148"/>
+    </row>
+    <row r="33" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="76" t="s">
         <v>105</v>
       </c>
-      <c r="B33" s="75">
+      <c r="B33" s="77">
+        <v>241</v>
+      </c>
+      <c r="C33" s="148">
+        <v>0.1205</v>
+      </c>
+      <c r="D33" s="148"/>
+      <c r="E33" s="148"/>
+      <c r="F33" s="148"/>
+      <c r="G33" s="148"/>
+      <c r="H33" s="148"/>
+      <c r="I33" s="148"/>
+      <c r="J33" s="148"/>
+    </row>
+    <row r="34" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="76" t="s">
+        <v>106</v>
+      </c>
+      <c r="B34" s="77">
         <v>283</v>
       </c>
-      <c r="C33" s="76">
+      <c r="C34" s="148">
         <v>0.14149999999999999</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="74" t="s">
-        <v>106</v>
-      </c>
-      <c r="B34" s="75">
+      <c r="D34" s="148"/>
+      <c r="E34" s="148"/>
+      <c r="F34" s="148"/>
+      <c r="G34" s="148"/>
+      <c r="H34" s="148"/>
+      <c r="I34" s="148"/>
+      <c r="J34" s="148"/>
+    </row>
+    <row r="35" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="76" t="s">
+        <v>107</v>
+      </c>
+      <c r="B35" s="77">
         <v>261</v>
       </c>
-      <c r="C34" s="76">
+      <c r="C35" s="148">
         <v>0.1305</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="77" t="s">
-        <v>107</v>
-      </c>
-      <c r="B35" s="78">
-        <v>212</v>
-      </c>
-      <c r="C35" s="79">
-        <v>0.106</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="77" t="s">
+      <c r="D35" s="148"/>
+      <c r="E35" s="148"/>
+      <c r="F35" s="148"/>
+      <c r="G35" s="148"/>
+      <c r="H35" s="148"/>
+      <c r="I35" s="148"/>
+      <c r="J35" s="148"/>
+    </row>
+    <row r="36" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="76" t="s">
         <v>108</v>
       </c>
-      <c r="B36" s="78">
-        <v>160</v>
-      </c>
-      <c r="C36" s="79">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="77" t="s">
+      <c r="B36" s="77">
+        <v>211</v>
+      </c>
+      <c r="C36" s="148">
+        <v>0.1055</v>
+      </c>
+      <c r="D36" s="148"/>
+      <c r="E36" s="148"/>
+      <c r="F36" s="148"/>
+      <c r="G36" s="148"/>
+      <c r="H36" s="148"/>
+      <c r="I36" s="148"/>
+      <c r="J36" s="148"/>
+    </row>
+    <row r="37" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="78" t="s">
         <v>109</v>
       </c>
-      <c r="B37" s="78">
-        <v>97</v>
-      </c>
-      <c r="C37" s="79">
-        <v>4.8500000000000001E-2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="80" t="s">
+      <c r="B37" s="79">
+        <v>161</v>
+      </c>
+      <c r="C37" s="149">
+        <v>8.0500000000000002E-2</v>
+      </c>
+      <c r="D37" s="149"/>
+      <c r="E37" s="149"/>
+      <c r="F37" s="149"/>
+      <c r="G37" s="149"/>
+      <c r="H37" s="149"/>
+      <c r="I37" s="149"/>
+      <c r="J37" s="149"/>
+    </row>
+    <row r="38" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="78" t="s">
         <v>110</v>
       </c>
-      <c r="B38" s="81">
+      <c r="B38" s="79">
+        <v>95</v>
+      </c>
+      <c r="C38" s="149">
+        <v>4.7500000000000001E-2</v>
+      </c>
+      <c r="D38" s="149"/>
+      <c r="E38" s="149"/>
+      <c r="F38" s="149"/>
+      <c r="G38" s="149"/>
+      <c r="H38" s="149"/>
+      <c r="I38" s="149"/>
+      <c r="J38" s="149"/>
+    </row>
+    <row r="39" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="78" t="s">
+        <v>111</v>
+      </c>
+      <c r="B39" s="79">
         <v>74</v>
       </c>
-      <c r="C38" s="82">
+      <c r="C39" s="149">
         <v>3.6999999999999998E-2</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="80" t="s">
-        <v>111</v>
-      </c>
-      <c r="B39" s="81">
-        <v>35</v>
-      </c>
-      <c r="C39" s="82">
-        <v>1.7500000000000002E-2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D39" s="149"/>
+      <c r="E39" s="149"/>
+      <c r="F39" s="149"/>
+      <c r="G39" s="149"/>
+      <c r="H39" s="149"/>
+      <c r="I39" s="149"/>
+      <c r="J39" s="149"/>
+    </row>
+    <row r="40" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="80" t="s">
         <v>112</v>
       </c>
       <c r="B40" s="81">
-        <v>16</v>
-      </c>
-      <c r="C40" s="82">
-        <v>8.0000000000000002E-3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="C40" s="150">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="D40" s="150"/>
+      <c r="E40" s="150"/>
+      <c r="F40" s="150"/>
+      <c r="G40" s="150"/>
+      <c r="H40" s="150"/>
+      <c r="I40" s="150"/>
+      <c r="J40" s="150"/>
+    </row>
+    <row r="41" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="80" t="s">
         <v>113</v>
       </c>
       <c r="B41" s="81">
-        <v>6</v>
-      </c>
-      <c r="C41" s="82">
-        <v>3.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="C41" s="150">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="D41" s="150"/>
+      <c r="E41" s="150"/>
+      <c r="F41" s="150"/>
+      <c r="G41" s="150"/>
+      <c r="H41" s="150"/>
+      <c r="I41" s="150"/>
+      <c r="J41" s="150"/>
+    </row>
+    <row r="42" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="80" t="s">
         <v>114</v>
       </c>
       <c r="B42" s="81">
-        <v>3</v>
-      </c>
-      <c r="C42" s="82">
-        <v>1.5E-3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="C42" s="150">
+        <v>3.5000000000000001E-3</v>
+      </c>
+      <c r="D42" s="150"/>
+      <c r="E42" s="150"/>
+      <c r="F42" s="150"/>
+      <c r="G42" s="150"/>
+      <c r="H42" s="150"/>
+      <c r="I42" s="150"/>
+      <c r="J42" s="150"/>
+    </row>
+    <row r="43" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="80" t="s">
         <v>115</v>
       </c>
       <c r="B43" s="81">
-        <v>0</v>
-      </c>
-      <c r="C43" s="82">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="C43" s="150">
+        <v>1.5E-3</v>
+      </c>
+      <c r="D43" s="150"/>
+      <c r="E43" s="150"/>
+      <c r="F43" s="150"/>
+      <c r="G43" s="150"/>
+      <c r="H43" s="150"/>
+      <c r="I43" s="150"/>
+      <c r="J43" s="150"/>
+    </row>
+    <row r="44" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="80" t="s">
         <v>116</v>
       </c>
       <c r="B44" s="81">
+        <v>0</v>
+      </c>
+      <c r="C44" s="150">
+        <v>0</v>
+      </c>
+      <c r="D44" s="150"/>
+      <c r="E44" s="150"/>
+      <c r="F44" s="150"/>
+      <c r="G44" s="150"/>
+      <c r="H44" s="150"/>
+      <c r="I44" s="150"/>
+      <c r="J44" s="150"/>
+    </row>
+    <row r="45" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="80" t="s">
+        <v>117</v>
+      </c>
+      <c r="B45" s="81">
         <v>1</v>
       </c>
-      <c r="C44" s="82">
+      <c r="C45" s="150">
         <v>5.0000000000000001E-4</v>
       </c>
+      <c r="D45" s="150"/>
+      <c r="E45" s="150"/>
+      <c r="F45" s="150"/>
+      <c r="G45" s="150"/>
+      <c r="H45" s="150"/>
+      <c r="I45" s="150"/>
+      <c r="J45" s="150"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="44">
+    <mergeCell ref="C42:J42"/>
+    <mergeCell ref="C43:J43"/>
+    <mergeCell ref="C44:J44"/>
+    <mergeCell ref="C45:J45"/>
+    <mergeCell ref="C37:J37"/>
+    <mergeCell ref="C38:J38"/>
+    <mergeCell ref="C39:J39"/>
+    <mergeCell ref="C40:J40"/>
+    <mergeCell ref="C41:J41"/>
+    <mergeCell ref="C32:J32"/>
+    <mergeCell ref="C33:J33"/>
+    <mergeCell ref="C34:J34"/>
+    <mergeCell ref="C35:J35"/>
+    <mergeCell ref="C36:J36"/>
+    <mergeCell ref="C27:J27"/>
+    <mergeCell ref="C28:J28"/>
+    <mergeCell ref="C29:J29"/>
+    <mergeCell ref="C30:J30"/>
+    <mergeCell ref="C31:J31"/>
+    <mergeCell ref="A22:J22"/>
+    <mergeCell ref="A23:J23"/>
+    <mergeCell ref="C24:J24"/>
+    <mergeCell ref="C25:J25"/>
+    <mergeCell ref="C26:J26"/>
     <mergeCell ref="C17:J17"/>
     <mergeCell ref="C18:J18"/>
     <mergeCell ref="C19:J19"/>
     <mergeCell ref="C20:J20"/>
-    <mergeCell ref="A22:J22"/>
+    <mergeCell ref="C21:J21"/>
     <mergeCell ref="C12:J12"/>
     <mergeCell ref="C13:J13"/>
     <mergeCell ref="C14:J14"/>
     <mergeCell ref="C15:J15"/>
     <mergeCell ref="C16:J16"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="A10:J10"/>
-    <mergeCell ref="C11:J11"/>
+    <mergeCell ref="C6:J6"/>
+    <mergeCell ref="C7:J7"/>
+    <mergeCell ref="C8:J8"/>
+    <mergeCell ref="C9:J9"/>
+    <mergeCell ref="A11:J11"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="D3:J3"/>
-    <mergeCell ref="D4:J4"/>
-    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="C3:J3"/>
+    <mergeCell ref="C4:J4"/>
+    <mergeCell ref="C5:J5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -4493,305 +4877,430 @@
   <sheetPr>
     <tabColor rgb="FFEF5350"/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
-    <col min="2" max="5" width="16" customWidth="1"/>
-    <col min="6" max="7" width="18" customWidth="1"/>
+    <col min="2" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="98" t="s">
-        <v>117</v>
-      </c>
-      <c r="B1" s="98"/>
-      <c r="C1" s="98"/>
-      <c r="D1" s="98"/>
-      <c r="E1" s="98"/>
-      <c r="F1" s="98"/>
-      <c r="G1" s="98"/>
-      <c r="H1" s="98"/>
-    </row>
-    <row r="2" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="109" t="s">
+    <row r="1" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="136" t="s">
         <v>118</v>
       </c>
-      <c r="B2" s="109"/>
-      <c r="C2" s="109"/>
-      <c r="D2" s="109"/>
-      <c r="E2" s="109"/>
-      <c r="F2" s="109"/>
-      <c r="G2" s="109"/>
-      <c r="H2" s="109"/>
-    </row>
-    <row r="3" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="59" t="s">
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
+      <c r="I1" s="53">
+        <f ca="1">'Matriz de Sensibilidad'!$B$4</f>
+        <v>999.47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="151" t="s">
         <v>119</v>
       </c>
-      <c r="B3" s="59" t="s">
+      <c r="B2" s="151"/>
+      <c r="C2" s="151"/>
+      <c r="D2" s="151"/>
+      <c r="E2" s="151"/>
+      <c r="F2" s="151"/>
+      <c r="G2" s="151"/>
+      <c r="H2" s="151"/>
+      <c r="I2" s="82">
+        <f ca="1">'Matriz de Sensibilidad'!$D$4</f>
+        <v>52.464199999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="61" t="s">
         <v>120</v>
       </c>
-      <c r="C3" s="59" t="s">
+      <c r="B3" s="61" t="s">
         <v>121</v>
       </c>
-      <c r="D3" s="59" t="s">
+      <c r="C3" s="61" t="s">
         <v>122</v>
       </c>
-      <c r="E3" s="59" t="s">
+      <c r="D3" s="61" t="s">
         <v>123</v>
       </c>
-      <c r="F3" s="59" t="s">
+      <c r="E3" s="61" t="s">
         <v>124</v>
       </c>
-      <c r="G3" s="59" t="s">
+      <c r="F3" s="61" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G3" s="61" t="s">
+        <v>126</v>
+      </c>
+      <c r="H3" s="61" t="s">
+        <v>127</v>
+      </c>
+      <c r="I3">
+        <f ca="1">'Matriz de Sensibilidad'!$B$4/'Matriz de Sensibilidad'!$D$4</f>
+        <v>19.050514446041301</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="83" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B4" s="84">
-        <v>109.2</v>
+        <f ca="1">$I$3*15*(1-0*0.06)</f>
+        <v>285.75771669061953</v>
       </c>
       <c r="C4" s="85">
-        <v>780</v>
+        <f t="shared" ref="C4:C10" ca="1" si="0">$I$1</f>
+        <v>999.47</v>
       </c>
       <c r="D4" s="86">
-        <v>819</v>
+        <f ca="1">$I$3*60*(1-0*0.06)</f>
+        <v>1143.0308667624781</v>
       </c>
       <c r="E4" s="87">
-        <v>-670.8</v>
+        <f t="shared" ref="E4:E10" ca="1" si="1">B4-$I$1</f>
+        <v>-713.7122833093805</v>
       </c>
       <c r="F4" s="86">
-        <v>39</v>
+        <f t="shared" ref="F4:F10" ca="1" si="2">D4-$I$1</f>
+        <v>143.5608667624781</v>
       </c>
       <c r="G4" s="88">
-        <v>709.8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="89" t="s">
-        <v>127</v>
-      </c>
-      <c r="B5" s="90">
-        <v>234</v>
-      </c>
-      <c r="C5" s="91">
-        <v>780</v>
-      </c>
-      <c r="D5" s="92">
-        <v>936</v>
-      </c>
-      <c r="E5" s="93">
-        <v>-546</v>
-      </c>
-      <c r="F5" s="92">
-        <v>156</v>
-      </c>
-      <c r="G5" s="94">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="83" t="s">
-        <v>128</v>
-      </c>
-      <c r="B6" s="84">
-        <v>468</v>
-      </c>
-      <c r="C6" s="85">
-        <v>780</v>
-      </c>
-      <c r="D6" s="86">
-        <v>858</v>
-      </c>
-      <c r="E6" s="87">
-        <v>-312</v>
-      </c>
-      <c r="F6" s="86">
-        <v>78</v>
-      </c>
-      <c r="G6" s="88">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="89" t="s">
+        <f t="shared" ref="G4:G10" ca="1" si="3">D4-B4</f>
+        <v>857.27315007185859</v>
+      </c>
+      <c r="H4" s="89">
+        <f t="shared" ref="H4:H10" ca="1" si="4">(B4-$I$1)/$I$1</f>
+        <v>-0.71409075140762657</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="90" t="s">
         <v>129</v>
       </c>
-      <c r="B7" s="90">
-        <v>468</v>
-      </c>
-      <c r="C7" s="91">
-        <v>780</v>
-      </c>
-      <c r="D7" s="92">
-        <v>842.4</v>
-      </c>
-      <c r="E7" s="93">
-        <v>-312</v>
-      </c>
-      <c r="F7" s="92">
-        <v>62.4</v>
-      </c>
-      <c r="G7" s="94">
-        <v>374.4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="83" t="s">
+      <c r="B5" s="91">
+        <f ca="1">$I$3*$I$2*(1-0.05*0.06)</f>
+        <v>996.47158999999999</v>
+      </c>
+      <c r="C5" s="92">
+        <f t="shared" ca="1" si="0"/>
+        <v>999.47</v>
+      </c>
+      <c r="D5" s="93">
+        <f ca="1">$I$3*$I$2*(1+0.005*0.06)</f>
+        <v>999.76984100000004</v>
+      </c>
+      <c r="E5" s="94">
+        <f t="shared" ca="1" si="1"/>
+        <v>-2.9984100000000353</v>
+      </c>
+      <c r="F5" s="93">
+        <f t="shared" ca="1" si="2"/>
+        <v>0.2998410000000149</v>
+      </c>
+      <c r="G5" s="95">
+        <f t="shared" ca="1" si="3"/>
+        <v>3.2982510000000502</v>
+      </c>
+      <c r="H5" s="96">
+        <f t="shared" ca="1" si="4"/>
+        <v>-3.0000000000000352E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="97" t="s">
         <v>130</v>
       </c>
-      <c r="B8" s="84">
-        <v>556.91999999999996</v>
-      </c>
-      <c r="C8" s="85">
-        <v>780</v>
-      </c>
-      <c r="D8" s="86">
-        <v>803.4</v>
-      </c>
-      <c r="E8" s="87">
-        <v>-223.08</v>
-      </c>
-      <c r="F8" s="86">
-        <v>23.400000000000102</v>
-      </c>
-      <c r="G8" s="88">
-        <v>246.48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="89" t="s">
+      <c r="B6" s="98">
+        <f ca="1">$I$3*0.6*$I$2</f>
+        <v>599.68200000000002</v>
+      </c>
+      <c r="C6" s="99">
+        <f t="shared" ca="1" si="0"/>
+        <v>999.47</v>
+      </c>
+      <c r="D6" s="100">
+        <f ca="1">$I$3*1.1*$I$2</f>
+        <v>1099.4170000000001</v>
+      </c>
+      <c r="E6" s="101">
+        <f t="shared" ca="1" si="1"/>
+        <v>-399.78800000000001</v>
+      </c>
+      <c r="F6" s="100">
+        <f t="shared" ca="1" si="2"/>
+        <v>99.947000000000116</v>
+      </c>
+      <c r="G6" s="102">
+        <f t="shared" ca="1" si="3"/>
+        <v>499.73500000000013</v>
+      </c>
+      <c r="H6" s="103">
+        <f t="shared" ca="1" si="4"/>
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="104" t="s">
         <v>131</v>
       </c>
-      <c r="B9" s="90">
-        <v>545.67240000000004</v>
-      </c>
-      <c r="C9" s="91">
-        <v>780</v>
-      </c>
-      <c r="D9" s="92">
-        <v>780</v>
-      </c>
-      <c r="E9" s="93">
-        <v>-234.32759999999999</v>
-      </c>
-      <c r="F9" s="92">
+      <c r="B7" s="105">
+        <f ca="1">$I$3*0.2*35</f>
+        <v>133.35360112228912</v>
+      </c>
+      <c r="C7" s="106">
+        <f t="shared" ca="1" si="0"/>
+        <v>999.47</v>
+      </c>
+      <c r="D7" s="107">
+        <f ca="1">$I$3*1.05*$I$2</f>
+        <v>1049.4435000000001</v>
+      </c>
+      <c r="E7" s="108">
+        <f t="shared" ca="1" si="1"/>
+        <v>-866.11639887771094</v>
+      </c>
+      <c r="F7" s="107">
+        <f t="shared" ca="1" si="2"/>
+        <v>49.973500000000058</v>
+      </c>
+      <c r="G7" s="109">
+        <f t="shared" ca="1" si="3"/>
+        <v>916.08989887771099</v>
+      </c>
+      <c r="H7" s="110">
+        <f t="shared" ca="1" si="4"/>
+        <v>-0.86657568399022578</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="111" t="s">
+        <v>132</v>
+      </c>
+      <c r="B8" s="112">
+        <f ca="1">$I$3*0.75*40</f>
+        <v>571.51543338123906</v>
+      </c>
+      <c r="C8" s="113">
+        <f t="shared" ca="1" si="0"/>
+        <v>999.47</v>
+      </c>
+      <c r="D8" s="114">
+        <f ca="1">$I$3*1.08*$I$2</f>
+        <v>1079.4276000000002</v>
+      </c>
+      <c r="E8" s="115">
+        <f t="shared" ca="1" si="1"/>
+        <v>-427.95456661876096</v>
+      </c>
+      <c r="F8" s="114">
+        <f t="shared" ca="1" si="2"/>
+        <v>79.957600000000184</v>
+      </c>
+      <c r="G8" s="116">
+        <f t="shared" ca="1" si="3"/>
+        <v>507.91216661876115</v>
+      </c>
+      <c r="H8" s="117">
+        <f t="shared" ca="1" si="4"/>
+        <v>-0.42818150281525302</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="118" t="s">
+        <v>133</v>
+      </c>
+      <c r="B9" s="119">
+        <f ca="1">$I$3*0.85*42</f>
+        <v>680.10336572367441</v>
+      </c>
+      <c r="C9" s="120">
+        <f t="shared" ca="1" si="0"/>
+        <v>999.47</v>
+      </c>
+      <c r="D9" s="121">
+        <f ca="1">$I$3*1.03*$I$2</f>
+        <v>1029.4541000000002</v>
+      </c>
+      <c r="E9" s="122">
+        <f t="shared" ca="1" si="1"/>
+        <v>-319.36663427632561</v>
+      </c>
+      <c r="F9" s="121">
+        <f t="shared" ca="1" si="2"/>
+        <v>29.984100000000126</v>
+      </c>
+      <c r="G9" s="123">
+        <f t="shared" ca="1" si="3"/>
+        <v>349.35073427632574</v>
+      </c>
+      <c r="H9" s="124">
+        <f t="shared" ca="1" si="4"/>
+        <v>-0.31953598835015118</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="125" t="s">
+        <v>134</v>
+      </c>
+      <c r="B10" s="126">
+        <f ca="1">$I$3*35*(1-0.01*0.06)</f>
+        <v>666.36794480807873</v>
+      </c>
+      <c r="C10" s="127">
+        <f t="shared" ca="1" si="0"/>
+        <v>999.47</v>
+      </c>
+      <c r="D10" s="128">
+        <f ca="1">$I$3*$I$2*(1+0*0.06)</f>
+        <v>999.47</v>
+      </c>
+      <c r="E10" s="129">
+        <f t="shared" ca="1" si="1"/>
+        <v>-333.10205519192129</v>
+      </c>
+      <c r="F10" s="128">
+        <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
-      <c r="G9" s="94">
-        <v>234.32759999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="83" t="s">
+      <c r="G10" s="130">
+        <f t="shared" ca="1" si="3"/>
+        <v>333.10205519192129</v>
+      </c>
+      <c r="H10" s="131">
+        <f t="shared" ca="1" si="4"/>
+        <v>-0.33327869289915785</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="152" t="s">
+        <v>135</v>
+      </c>
+      <c r="B12" s="152"/>
+      <c r="C12" s="152"/>
+      <c r="D12" s="152"/>
+      <c r="E12" s="152"/>
+      <c r="F12" s="152"/>
+      <c r="G12" s="152"/>
+      <c r="H12" s="152"/>
+    </row>
+    <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>136</v>
+      </c>
+      <c r="B13" s="132">
+        <f t="shared" ref="B13:C19" ca="1" si="5">E4</f>
+        <v>-713.7122833093805</v>
+      </c>
+      <c r="C13" s="132">
+        <f t="shared" ca="1" si="5"/>
+        <v>143.5608667624781</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>129</v>
+      </c>
+      <c r="B14" s="132">
+        <f t="shared" ca="1" si="5"/>
+        <v>-2.9984100000000353</v>
+      </c>
+      <c r="C14" s="132">
+        <f t="shared" ca="1" si="5"/>
+        <v>0.2998410000000149</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>130</v>
+      </c>
+      <c r="B15" s="132">
+        <f t="shared" ca="1" si="5"/>
+        <v>-399.78800000000001</v>
+      </c>
+      <c r="C15" s="132">
+        <f t="shared" ca="1" si="5"/>
+        <v>99.947000000000116</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>137</v>
+      </c>
+      <c r="B16" s="132">
+        <f t="shared" ca="1" si="5"/>
+        <v>-866.11639887771094</v>
+      </c>
+      <c r="C16" s="132">
+        <f t="shared" ca="1" si="5"/>
+        <v>49.973500000000058</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>132</v>
       </c>
-      <c r="B10" s="84">
-        <v>777.66</v>
-      </c>
-      <c r="C10" s="85">
-        <v>780</v>
-      </c>
-      <c r="D10" s="86">
-        <v>780.23400000000004</v>
-      </c>
-      <c r="E10" s="87">
-        <v>-2.3400000000000301</v>
-      </c>
-      <c r="F10" s="86">
-        <v>0.23399999999992399</v>
-      </c>
-      <c r="G10" s="88">
-        <v>2.5739999999999599</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="99" t="s">
-        <v>133</v>
-      </c>
-      <c r="B30" s="99"/>
-      <c r="C30" s="99"/>
-      <c r="D30" s="99"/>
-      <c r="E30" s="99"/>
-      <c r="F30" s="99"/>
-      <c r="G30" s="99"/>
-      <c r="H30" s="99"/>
-    </row>
-    <row r="31" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="110" t="s">
-        <v>134</v>
-      </c>
-      <c r="B31" s="110"/>
-      <c r="C31" s="110"/>
-      <c r="D31" s="110"/>
-      <c r="E31" s="110"/>
-      <c r="F31" s="110"/>
-      <c r="G31" s="110"/>
-      <c r="H31" s="110"/>
-    </row>
-    <row r="32" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="111" t="s">
-        <v>135</v>
-      </c>
-      <c r="B32" s="111"/>
-      <c r="C32" s="111"/>
-      <c r="D32" s="111"/>
-      <c r="E32" s="111"/>
-      <c r="F32" s="111"/>
-      <c r="G32" s="111"/>
-      <c r="H32" s="111"/>
-    </row>
-    <row r="33" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="110" t="s">
-        <v>136</v>
-      </c>
-      <c r="B33" s="110"/>
-      <c r="C33" s="110"/>
-      <c r="D33" s="110"/>
-      <c r="E33" s="110"/>
-      <c r="F33" s="110"/>
-      <c r="G33" s="110"/>
-      <c r="H33" s="110"/>
-    </row>
-    <row r="34" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="111" t="s">
-        <v>137</v>
-      </c>
-      <c r="B34" s="111"/>
-      <c r="C34" s="111"/>
-      <c r="D34" s="111"/>
-      <c r="E34" s="111"/>
-      <c r="F34" s="111"/>
-      <c r="G34" s="111"/>
-      <c r="H34" s="111"/>
-    </row>
-    <row r="35" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="110" t="s">
+      <c r="B17" s="132">
+        <f t="shared" ca="1" si="5"/>
+        <v>-427.95456661876096</v>
+      </c>
+      <c r="C17" s="132">
+        <f t="shared" ca="1" si="5"/>
+        <v>79.957600000000184</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>138</v>
       </c>
-      <c r="B35" s="110"/>
-      <c r="C35" s="110"/>
-      <c r="D35" s="110"/>
-      <c r="E35" s="110"/>
-      <c r="F35" s="110"/>
-      <c r="G35" s="110"/>
-      <c r="H35" s="110"/>
+      <c r="B18" s="132">
+        <f t="shared" ca="1" si="5"/>
+        <v>-319.36663427632561</v>
+      </c>
+      <c r="C18" s="132">
+        <f t="shared" ca="1" si="5"/>
+        <v>29.984100000000126</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>139</v>
+      </c>
+      <c r="B19" s="132">
+        <f t="shared" ca="1" si="5"/>
+        <v>-333.10205519192129</v>
+      </c>
+      <c r="C19" s="132">
+        <f t="shared" ca="1" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="153" t="s">
+        <v>140</v>
+      </c>
+      <c r="B39" s="153"/>
+      <c r="C39" s="153"/>
+      <c r="D39" s="153"/>
+      <c r="E39" s="153"/>
+      <c r="F39" s="153"/>
+      <c r="G39" s="153"/>
+      <c r="H39" s="153"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A33:H33"/>
-    <mergeCell ref="A34:H34"/>
-    <mergeCell ref="A35:H35"/>
+  <mergeCells count="4">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A39:H39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/Simulador_Riesgos_Costco_BlackSwan.xlsx
+++ b/Simulador_Riesgos_Costco_BlackSwan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luism\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55AC3C75-66B6-4C12-A6FD-E73FC14AB7F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D135443-2079-43AE-9BCA-C26CAA161FB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
